--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>63.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>54.14</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>54.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>16001469.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>19996474.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>19996474.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>55086319.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25070064.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25070064.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-3944310.55324452</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>16001469</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>16001469.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>64.56</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>53.73</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>53.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>13807588.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>23777429.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>23777429.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>54425533.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>24750839.9</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>24750839.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-2733457.873315699</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>13807588</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>13807588.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>54.14000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>53.42</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>53.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>32443436.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>31680134.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>31680134.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>54178663.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>24499720.74</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>24499720.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-670986.1565132588</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>32443436</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>32443436.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>56.73999999999999</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>53.21</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>53.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>13607992.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>43824688.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>43824688.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>52778418.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>23864128.78</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>23864128.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>302667.8016514182</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>13607992</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>13607992.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>67.96</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>52.97</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>52.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>24121887.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>84772306.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>84772306.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>51955402.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>23598443.82</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>23598443.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>3700875.748970546</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>24121887</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>24121887.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>63.14</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>68.39</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>52.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>52.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>34906243.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>90176165.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>90176165.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>51086664.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>23117663.44</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>23117663.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>7296795.646963216</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>34906243</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>34906243.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>64.60000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>52.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>53321114.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>85073637.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>85073637.59999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>49187526.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>22420646.66</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>22420646.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>11017757.51384691</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>53321114</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>53321114.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>65.96000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>68.44</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>52.04</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>52.04</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>93166208.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>76677193.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>76677193</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>45691253.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>21358539.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>21358539.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>13966904.09104338</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>93166208</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>93166208.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>65.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>67.71</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>51.55</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51.55</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>218346081.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>61732148.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>61732148</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>37735256.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>19506206.82</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>19506206.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>13412035.41235821</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>218346081</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>218346081.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>65.78</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>66.41</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>50.93</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>50.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>51141181.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>19138497.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>19138497.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>18083906.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>15141675.98</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>15141675.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1271764.643347684</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>51141181</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>51141181.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>66.4</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>65.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>50.36</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>50.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>9393604.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>11997164.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>11997164.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15519974.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>14120970.28</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>14120970.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-4288390.985665116</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>9393604</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>9393604.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>52.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>56.01</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>61.9</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>61.9</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>69216381.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>61829613.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>61829613.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>74653108.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>168131289.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>168131289.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-8411909.244457036</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>69216381</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>69216381.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>51.64</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>56.37</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>62.23</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>62.23</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>52553235.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>63464668.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>63464668</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>94912194.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>178098033.32</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>178098033.32</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-9314837.648330897</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>52553235</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>52553235.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>51.68000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>56.81</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>62.63</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>62.63</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>45222687.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>76632523.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>76632523.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>95793491.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>184959890.74</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>184959890.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-8486725.523567438</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>45222687</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>45222687.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>52.36</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>57.28</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>63.02</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>63.02</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>56513860.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>84504591.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>84504591.40000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>98072242.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>193477053.86</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>193477053.86</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-6215195.005206525</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>56513860</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>56513860.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>53.42</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>57.74</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>63.45</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>63.45</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>85641903.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>83775801.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>83775801.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>100864335.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>209527912.74</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>209527912.74</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3957948.693076432</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>85641903</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>85641903.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>54.3</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>58.16</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>63.91</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>63.91</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>77391655.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>87476602.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>87476602.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>97242313.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>224649814.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>224649814.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-3712817.543852121</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>77391655</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>77391655.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>55.67999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>58.64</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>118392514.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>126359721.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>126359721</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>95330141.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>253291338.6</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>253291338.6</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-2346074.418394119</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>118392514</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>118392514.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>56.64</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>59.06</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>64.99</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>64.98999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>84583025.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>114954458.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>114954458.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>90385751.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>305232631.7</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>305232631.7</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-4702745.045654312</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>84583025</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>84583025.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>57.17999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>59.32</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>65.44</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>65.44</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>52869912.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>111639893.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>111639893.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>89954407.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>408137545.72</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>408137545.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4279016.940109804</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>52869912</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>52869912.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>57.58</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>65.85</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>65.84999999999999</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>104145908.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>117952868.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>117952868.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>89741248.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>458871880.9</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>458871880.9</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-123035.5057565868</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>104145908</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>104145908.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>58.04</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>66.17</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>66.17</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>271807246.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>107008024.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>107008024.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>87743013.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>466563097.14</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>466563097.14</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>324618.2399536073</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>271807246</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>271807246.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,21 +10517,17 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
       <c r="AP24" t="inlineStr">
         <is>
           <t>-19.58</t>
@@ -10704,20 +10568,16 @@
           <t>201657416.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>252360977.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>252360977.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>282417854.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>423553251.3</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>423553251.3</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-36974729.3629033</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>201657416</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>201657416.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>39.04000000000001</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>39.71</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>40.26</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>195613562.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>255801795.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>255801795.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>285762642.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>457544220.78</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>457544220.78</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-35925485.46414912</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>195613562</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>195613562.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>39.16</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>40.4</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>188357162.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>277240412.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>277240412.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>297413036.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>528814161.92</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>528814161.92</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-32495956.77078068</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>188357162</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>188357162.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>39.25</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>39.94</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>40.53</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>355837208.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>346026858.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>346026858.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>290442567.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>558638708.96</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>558638708.96</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-25658588.75272644</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>355837208</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>355837208.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>40.66</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>40.66</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>320339540.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>322944767.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>322944767</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>273188557.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>613979125.7</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>613979125.7</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-32918832.62862295</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>320339540</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>320339540.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>218861506.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>312474732.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>312474732.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>262014209.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>631667121.94</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>631667121.9400001</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-38311615.42888141</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>218861506</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>218861506.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>39.55</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>39.83</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>40.77</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>40.77</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>302806648.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>315723489.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>315723489</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>267936291.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>654424013.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>654424013.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-33774672.37821913</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>302806648</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>302806648.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>39.57000000000001</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>40.87</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>40.87</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>532289392.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>317585660.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>317585660.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>263274442.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>673739372.28</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>673739372.28</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-35081209.22090816</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>532289392</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>532289392.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>39.51000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>39.76</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>41</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>240426749.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>234858276.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>234858276.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>236240878.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>679732391.62</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>679732391.62</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-60282226.95257431</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>240426749</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>240426749.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>267989366.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>223432348.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>223432348.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>270578244.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>693037521.34</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>693037521.34</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-62859746.71379119</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>267989366</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>267989366.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>39.72</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>41.21</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>235105290.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>211553687.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>211553687.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>317718579.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>694915339.42</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>694915339.42</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-67250064.3828941</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>235105290</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>235105290.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1886.002</t>
+          <t>5861.129</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>62.51</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>8.73</v>
+        <v>14.01</v>
       </c>
       <c r="AI2" t="n">
-        <v>16.75</v>
+        <v>19.46</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.14000000000001</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>64.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>59.5</v>
+        <v>60.47</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>52.36</t>
+          <t>52.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>74.97</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>4.31</v>
+        <v>5.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-67.34</t>
+          <t>-59.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>147976040.0</t>
+          <t>520200732.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>124392619.4</v>
+        <v>208793542</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>92989560.5</t>
+          <t>143409486.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>43230289.22</v>
+        <v>53628092.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>31403058</t>
+          <t>65384055</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>9084624.363967046</t>
+          <t>14806848.53907775</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>17495659.71883589</t>
+          <t>46279081.50218663</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>147976040.0</t>
+          <t>520200732.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>99.27</t>
+          <t>118.29</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1085.584</t>
+          <t>1886.002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.09</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,29 +1436,29 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.19</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.94</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.42</v>
+        <v>8.73</v>
       </c>
       <c r="AI3" t="n">
-        <v>15.4</v>
+        <v>16.75</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1467,35 +1467,35 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.25999999999999</t>
+          <t>75.14000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>63.48</v>
+        <v>64.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>58.69</v>
+        <v>59.5</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>52.36</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>74.97</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>3.46</v>
+        <v>4.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-73.46</t>
+          <t>-67.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>81829226.0</t>
+          <t>147976040.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>128975556.8</v>
+        <v>124392619.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>79572715.3</t>
+          <t>92989560.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>40283892.52</v>
+        <v>43230289.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>49402841</t>
+          <t>31403058</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7555345.208536347</t>
+          <t>9084624.363967046</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>15632857.75266211</t>
+          <t>17495659.71883589</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>81829226.0</t>
+          <t>147976040.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>81.22</t>
+          <t>99.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3016.632</t>
+          <t>1085.584</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.74</t>
+          <t>62.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>99.99</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>97.88</t>
+          <t>94.94</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>5.7</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>13.77</v>
+        <v>15.4</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>73.25999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>62.95</v>
+        <v>63.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>58.03</v>
+        <v>58.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>51.47</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>3.08</v>
+        <v>3.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-78.29</t>
+          <t>-73.46</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>232271576.0</t>
+          <t>81829226.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>119966563.4</v>
+        <v>128975556.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>74634136.3</t>
+          <t>79572715.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>38669578</v>
+        <v>40283892.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>45332427</t>
+          <t>49402841</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6086706.564149845</t>
+          <t>7555345.208536347</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>19500554.38124734</t>
+          <t>15632857.75266211</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>232271576.0</t>
+          <t>81829226.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>84.63</t>
+          <t>81.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>851.112</t>
+          <t>3016.632</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.40</t>
+          <t>60.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,38 +2259,38 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>51.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>93.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>4.09</v>
+        <v>5.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.32</v>
+        <v>13.77</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>62.66</v>
+        <v>62.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.34</v>
+        <v>58.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>51.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>87.85</t>
+          <t>87.89</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.06</t>
+          <t>-78.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>61690136.0</t>
+          <t>232271576.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>77250902.40000001</v>
+        <v>119966563.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>52767777.9</t>
+          <t>74634136.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>34035769.78</v>
+        <v>38669578</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24483124</t>
+          <t>45332427</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3647825.142859392</t>
+          <t>6086706.564149845</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>8210563.694181718</t>
+          <t>19500554.38124734</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>61690136.0</t>
+          <t>232271576.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>84.63</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1369.005</t>
+          <t>851.112</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.20</t>
+          <t>46.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.88</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>9.82</v>
+        <v>4.09</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.61</v>
+        <v>9.32</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>62.68</v>
+        <v>62.66</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.75</v>
+        <v>57.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>87.85</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-86.78</t>
+          <t>-83.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>98196119.0</t>
+          <t>61690136.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>78025431.59999999</v>
+        <v>77250902.40000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49010953.0</t>
+          <t>52767777.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>32815239.12</v>
+        <v>34035769.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>29014478</t>
+          <t>24483124</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2818236.315346242</t>
+          <t>3647825.142859392</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>10065354.00929575</t>
+          <t>8210563.694181718</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>98196119.0</t>
+          <t>61690136.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2419.8</t>
+          <t>1369.005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,74 +3008,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>18.77</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6.81</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>59.20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>11.51</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6.04</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>49.2</t>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>96.51</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>13.15</v>
+        <v>9.82</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.1</v>
+        <v>5.61</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>62.58</v>
+        <v>62.68</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.11</v>
+        <v>56.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>58.50</t>
+          <t>95.50</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-89.94</t>
+          <t>-86.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>170890727.0</t>
+          <t>98196119.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>61586501.6</v>
+        <v>78025431.59999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>42681965.4</t>
+          <t>49010953.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>30859208.5</v>
+        <v>32815239.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>18904536</t>
+          <t>29014478</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1500578.552809967</t>
+          <t>2818236.315346242</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8444222.209126666</t>
+          <t>10065354.00929575</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>170890727.0</t>
+          <t>98196119.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>76.34</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>72.7</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>66.9</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>72.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>568.603</t>
+          <t>2419.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,22 +3440,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,33 +3525,33 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>86.51</t>
+          <t>96.51</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>9.109999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>62.32</v>
+        <v>62.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>55.46</v>
+        <v>56.11</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.75</t>
+          <t>58.50</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.27</v>
+        <v>1.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-91.41</t>
+          <t>-89.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36784259.0</t>
+          <t>170890727.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>30169873.8</v>
+        <v>61586501.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>30925004.1</t>
+          <t>42681965.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>27452381.94</v>
+        <v>30859208.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-755130</t>
+          <t>18904536</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>238097.8880251125</t>
+          <t>1500578.552809967</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1961967.727155112</t>
+          <t>8444222.209126666</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>36784259.0</t>
+          <t>170890727.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>61.22</t>
+          <t>76.34</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>309.983</t>
+          <t>568.603</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.86</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>86.51</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>4.52</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AI9" t="n">
-        <v>-8.1</v>
+        <v>-2.8</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>62.57</v>
+        <v>62.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>54.94</v>
+        <v>55.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.53</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-138.48</t>
+          <t>-57.75</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-90.17</t>
+          <t>-91.41</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18693271.0</t>
+          <t>36784259.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>29301709.2</v>
+        <v>30169873.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>36563199.0</t>
+          <t>30925004.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26730293.76</v>
+        <v>27452381.94</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-7261489</t>
+          <t>-755130</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>638109.8180578805</t>
+          <t>238097.8880251125</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2389332.93158783</t>
+          <t>-1961967.727155112</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18693271.0</t>
+          <t>36784259.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>46.59</t>
+          <t>61.22</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1076.252</t>
+          <t>309.983</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-49.96</t>
+          <t>-19.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>6.82</v>
+        <v>4.52</v>
       </c>
       <c r="AI10" t="n">
-        <v>-11.48</v>
+        <v>-8.1</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>63.24</v>
+        <v>62.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>54.54</v>
+        <v>54.94</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>49.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-138.52</t>
+          <t>-138.48</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-86.76</t>
+          <t>-90.17</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>65562782.0</t>
+          <t>18693271.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>28284653.4</v>
+        <v>29301709.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>56528480.0</t>
+          <t>36563199.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26364431.12</v>
+        <v>26730293.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-28243826</t>
+          <t>-7261489</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1188553.954357101</t>
+          <t>638109.8180578805</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-976201.1903635785</t>
+          <t>-2389332.93158783</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>65562782.0</t>
+          <t>18693271.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.59</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>261.462</t>
+          <t>1076.252</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-49.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>11.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI11" t="n">
-        <v>-13.83</v>
+        <v>-11.48</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>17.88</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.98</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>63.82</v>
+        <v>63.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.14</v>
+        <v>54.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-135.34</t>
+          <t>-138.52</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.48</v>
+        <v>-0.38</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-82.18</t>
+          <t>-86.76</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16001469.0</t>
+          <t>65562782.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>19996474.4</v>
+        <v>28284653.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>55086319.9</t>
+          <t>56528480.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>25070064.28</v>
+        <v>26364431.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-35089845</t>
+          <t>-28243826</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1582145.79885177</t>
+          <t>1188553.954357101</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3944310.55324452</t>
+          <t>-976201.1903635785</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>16001469.0</t>
+          <t>65562782.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>256.039</t>
+          <t>261.462</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-56.31</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>3.53</v>
+        <v>11.27</v>
       </c>
       <c r="AI12" t="n">
-        <v>-16.67</v>
+        <v>-13.83</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>17.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>64.56</v>
+        <v>63.82</v>
       </c>
       <c r="AN12" t="n">
-        <v>53.73</v>
+        <v>54.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-140.35</t>
+          <t>-135.34</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.73</v>
+        <v>-0.48</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.15</t>
+          <t>-82.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6029672.382978723</t>
+          <t>7126374.118980169</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13807588.0</t>
+          <t>16001469.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>23777429.2</v>
+        <v>19996474.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>54425533.4</t>
+          <t>55086319.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>24750839.9</v>
+        <v>25070064.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-30648104</t>
+          <t>-35089845</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2586956.044687459</t>
+          <t>1582145.79885177</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2733457.873315699</t>
+          <t>-3944310.55324452</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13807588.0</t>
+          <t>16001469.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>950.913</t>
+          <t>4345.485</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,12 +5656,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5671,51 +5671,51 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>0.86</v>
+        <v>0.48</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.17</v>
+        <v>0.63</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>53.44</t>
+          <t>53.64</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>53.53</v>
+        <v>53.31</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.68</v>
+        <v>58.35</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>64.34</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>25.90</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.52</v>
+        <v>-1.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2.06</v>
+        <v>-1.92</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-129.38</t>
+          <t>-127.46</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>51389573.0</t>
+          <t>241580963.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>48724664.4</v>
+        <v>91586426.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>56389537.7</t>
+          <t>73625995.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>94910402.68000001</v>
+        <v>94352154.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-7664873</t>
+          <t>17960430</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-8187976.189208893</t>
+          <t>-5523991.529207927</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-5428809.767014176</t>
+          <t>9127924.100797385</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>51389573.0</t>
+          <t>241580963.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1676.756</t>
+          <t>950.913</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-27.74</t>
+          <t>-28.80</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>63.79</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>0.86</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.93</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.44</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>53.66</v>
+        <v>53.53</v>
       </c>
       <c r="AN14" t="n">
-        <v>59.04</v>
+        <v>58.68</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>64.56</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>25.90</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-1.68</v>
+        <v>-1.52</v>
       </c>
       <c r="AR14" t="n">
-        <v>-2.19</v>
+        <v>-2.06</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-131.28</t>
+          <t>-129.38</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>91257245.0</t>
+          <t>51389573.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>44407720</v>
+        <v>48724664.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>56505903.9</t>
+          <t>56389537.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>100012930.14</v>
+        <v>94910402.68000001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-12098183</t>
+          <t>-7664873</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-8689642.811426114</t>
+          <t>-8187976.189208893</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-5652608.872208774</t>
+          <t>-5428809.767014176</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>91257245.0</t>
+          <t>51389573.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-20.72</t>
+          <t>-21.88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,17 +6257,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>694.501</t>
+          <t>1676.756</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.46</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-30.52</t>
+          <t>-27.74</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,66 +6500,66 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>63.79</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-0.49</v>
+        <v>2.9</v>
       </c>
       <c r="AI15" t="n">
-        <v>-1.73</v>
+        <v>-0.93</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>53.79</v>
+        <v>53.66</v>
       </c>
       <c r="AN15" t="n">
-        <v>59.41</v>
+        <v>59.04</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>64.74</t>
+          <t>64.56</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-1.94</v>
+        <v>-1.68</v>
       </c>
       <c r="AR15" t="n">
-        <v>-2.32</v>
+        <v>-2.19</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-133.10</t>
+          <t>-131.28</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36487605.0</t>
+          <t>91257245.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>34537096.2</v>
+        <v>44407720</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>51902448.1</t>
+          <t>56505903.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>113313794.82</v>
+        <v>100012930.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-17365351</t>
+          <t>-12098183</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-9241830.80037472</t>
+          <t>-8689642.811426114</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-10041979.27705074</t>
+          <t>-5652608.872208774</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>36487605.0</t>
+          <t>91257245.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-23.77</t>
+          <t>-20.72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,17 +6679,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>697.194</t>
+          <t>694.501</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-33.46</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-30.52</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-0.3</v>
+        <v>-0.49</v>
       </c>
       <c r="AI16" t="n">
-        <v>-1.49</v>
+        <v>-1.73</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>53.26000000000001</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>54.06</v>
+        <v>53.79</v>
       </c>
       <c r="AN16" t="n">
-        <v>59.81</v>
+        <v>59.41</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>64.74</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>15.98</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-2.02</v>
+        <v>-1.94</v>
       </c>
       <c r="AR16" t="n">
-        <v>-2.41</v>
+        <v>-2.32</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.45</t>
+          <t>-133.10</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37216745.0</t>
+          <t>36487605.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>53753853</v>
+        <v>34537096.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>53905073.6</t>
+          <t>51902448.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>117903975.16</v>
+        <v>113313794.82</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-151220</t>
+          <t>-17365351</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-9096349.259160899</t>
+          <t>-9241830.80037472</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-10085690.59550174</t>
+          <t>-10041979.27705074</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>37216745.0</t>
+          <t>36487605.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.77</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,17 +7101,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>513.11</t>
+          <t>697.194</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,29 +7344,29 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>55.26</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>51.96</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.71</v>
+        <v>-0.3</v>
       </c>
       <c r="AI17" t="n">
-        <v>-2.07</v>
+        <v>-1.49</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -7375,35 +7375,35 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>53.26000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>54.41</v>
+        <v>54.06</v>
       </c>
       <c r="AN17" t="n">
-        <v>60.19</v>
+        <v>59.81</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>65.18</t>
+          <t>64.96</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>15.98</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-2.16</v>
+        <v>-2.02</v>
       </c>
       <c r="AR17" t="n">
-        <v>-2.51</v>
+        <v>-2.41</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-135.82</t>
+          <t>-134.45</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27272154.0</t>
+          <t>37216745.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>55665565.6</v>
+        <v>53753853</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>58747589.4</t>
+          <t>53905073.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>123114665.04</v>
+        <v>117903975.16</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3082023</t>
+          <t>-151220</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-8916469.016189838</t>
+          <t>-9096349.259160899</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-9866054.243449531</t>
+          <t>-10085690.59550174</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>27272154.0</t>
+          <t>37216745.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>561.719</t>
+          <t>513.11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.65</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,66 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>55.26</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-1.61</v>
+        <v>-0.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>-2.45</v>
+        <v>-2.07</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-9.66</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>53.36</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>54.7</v>
+        <v>54.41</v>
       </c>
       <c r="AN18" t="n">
-        <v>60.55</v>
+        <v>60.19</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>65.39</t>
+          <t>65.18</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-2.27</v>
+        <v>-2.16</v>
       </c>
       <c r="AR18" t="n">
-        <v>-2.59</v>
+        <v>-2.51</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-137.07</t>
+          <t>-135.82</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>29804851.0</t>
+          <t>27272154.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>64054411</v>
+        <v>55665565.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>63759539.5</t>
+          <t>58747589.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>135113982.2</v>
+        <v>123114665.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>294871</t>
+          <t>-3082023</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-8743817.156688076</t>
+          <t>-8916469.016189838</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-8134437.053251758</t>
+          <t>-9866054.243449531</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>29804851.0</t>
+          <t>27272154.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-23.91</t>
+          <t>-23.33</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>781.934</t>
+          <t>561.719</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.72</t>
+          <t>-30.65</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,66 +8188,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.08</v>
+        <v>-1.61</v>
       </c>
       <c r="AI19" t="n">
-        <v>-3.39</v>
+        <v>-2.45</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-9.66</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-7.10</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.36</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>55.02</v>
+        <v>54.7</v>
       </c>
       <c r="AN19" t="n">
-        <v>60.97</v>
+        <v>60.55</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>65.39</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>-2.35</v>
+        <v>-2.27</v>
       </c>
       <c r="AR19" t="n">
-        <v>-2.67</v>
+        <v>-2.59</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-138.21</t>
+          <t>-137.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>41904126.0</t>
+          <t>29804851.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>68604087.8</v>
+        <v>64054411</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>72618305.8</t>
+          <t>63759539.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>153754709.02</v>
+        <v>135113982.2</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4014218</t>
+          <t>294871</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-8854613.539131043</t>
+          <t>-8743817.156688076</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-5641542.993924513</t>
+          <t>-8134437.053251758</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>41904126.0</t>
+          <t>29804851.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-23.91</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2416.476</t>
+          <t>781.934</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.87</t>
+          <t>-29.72</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>3.49</v>
+        <v>0.08</v>
       </c>
       <c r="AI20" t="n">
-        <v>-4.77</v>
+        <v>-3.39</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-7.10</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>52.76000000000001</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>55.4</v>
+        <v>55.02</v>
       </c>
       <c r="AN20" t="n">
-        <v>61.31</v>
+        <v>60.97</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>65.86</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-2.48</v>
+        <v>-2.35</v>
       </c>
       <c r="AR20" t="n">
-        <v>-2.75</v>
+        <v>-2.67</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-139.37</t>
+          <t>-138.21</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>132571389.0</t>
+          <t>41904126.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>69267800</v>
+        <v>68604087.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>76886195.7</t>
+          <t>72618305.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>159195479.02</v>
+        <v>153754709.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-7618395</t>
+          <t>-4014218</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-9438808.183714049</t>
+          <t>-8854613.539131043</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3175132.980816871</t>
+          <t>-5641542.993924513</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>132571389.0</t>
+          <t>41904126.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-20.87</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>872.805</t>
+          <t>2416.476</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-21.56</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-29.72</t>
+          <t>-27.87</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>40.21</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>2.31</v>
+        <v>3.49</v>
       </c>
       <c r="AI21" t="n">
-        <v>-6.64</v>
+        <v>-4.77</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.76000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>61.58</v>
+        <v>61.31</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>65.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-2.76</v>
+        <v>-2.48</v>
       </c>
       <c r="AR21" t="n">
-        <v>-2.82</v>
+        <v>-2.75</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-140.33</t>
+          <t>-139.37</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>46775308.0</t>
+          <t>132571389.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>54056294.2</v>
+        <v>69267800</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>68916048.0</t>
+          <t>76886195.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>161104262.68</v>
+        <v>159195479.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-14859753</t>
+          <t>-7618395</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-10577658.22060445</t>
+          <t>-9438808.183714049</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-9252642.105633907</t>
+          <t>-3175132.980816871</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>46775308.0</t>
+          <t>132571389.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-20.87</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9313,7 +9313,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1305.786</t>
+          <t>872.805</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.18</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-29.72</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,38 +9454,38 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>40.21</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AI22" t="n">
-        <v>-7.16</v>
+        <v>-6.64</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -9494,26 +9494,26 @@
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>56.01</v>
+        <v>55.7</v>
       </c>
       <c r="AN22" t="n">
-        <v>61.9</v>
+        <v>61.58</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>66.08</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-2.93</v>
+        <v>-2.76</v>
       </c>
       <c r="AR22" t="n">
-        <v>-2.84</v>
+        <v>-2.82</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-140.55</t>
+          <t>-140.33</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>69216381.0</t>
+          <t>46775308.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>61829613.2</v>
+        <v>54056294.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>74653108.0</t>
+          <t>68916048.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>168131289.9</v>
+        <v>161104262.68</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-12823494</t>
+          <t>-14859753</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-10818570.24150818</t>
+          <t>-10577658.22060445</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-8411909.244457036</t>
+          <t>-9252642.105633907</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>69216381.0</t>
+          <t>46775308.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-22.75</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1014.347</t>
+          <t>1305.786</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.13</t>
+          <t>-17.18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-31.97</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-0.27</v>
+        <v>2.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>-8.390000000000001</v>
+        <v>-7.16</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.64</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>56.37</v>
+        <v>56.01</v>
       </c>
       <c r="AN23" t="n">
-        <v>62.23</v>
+        <v>61.9</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-3.12</v>
+        <v>-2.93</v>
       </c>
       <c r="AR23" t="n">
-        <v>-2.81</v>
+        <v>-2.84</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-140.21</t>
+          <t>-140.55</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>499035129.6822034</t>
+          <t>498842374.1318759</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>52553235.0</t>
+          <t>69216381.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>63464668</v>
+        <v>61829613.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>94912194.5</t>
+          <t>74653108.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>178098033.32</v>
+        <v>168131289.9</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-31447526</t>
+          <t>-12823494</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-11256144.96824475</t>
+          <t>-10818570.24150818</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-9314837.648330897</t>
+          <t>-8411909.244457036</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>52553235.0</t>
+          <t>69216381.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-22.75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>52.2</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5078.41</t>
+          <t>4525.385</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>-28.41</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>86.19</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1.45</v>
+        <v>0.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>39.52</v>
+        <v>39.53</v>
       </c>
       <c r="AN24" t="n">
-        <v>39.91</v>
+        <v>39.9</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>151.56</t>
+          <t>235.57</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-102.30</t>
+          <t>-101.45</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>204926741.0</t>
+          <t>182844267.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>265975032</v>
+        <v>184011981.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>258916931.1</t>
+          <t>257035616.2</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>378065815.02</v>
+        <v>375554827.68</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>7058100</t>
+          <t>-73023634</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-20401145.0830142</t>
+          <t>-20694159.92539793</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-19967004.72779879</t>
+          <t>-22305741.5585084</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>204926741.0</t>
+          <t>182844267.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5284.456</t>
+          <t>5078.41</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>0.53</v>
+        <v>1.45</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>39.47</v>
+        <v>39.52</v>
       </c>
       <c r="AN25" t="n">
         <v>39.91</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>82.20</t>
+          <t>151.56</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-103.18</t>
+          <t>-102.30</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>211636508.0</t>
+          <t>204926741.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>289039877.2</v>
+        <v>265975032</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>257985613.2</t>
+          <t>258916931.1</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>380318818.8</v>
+        <v>378065815.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>31054264</t>
+          <t>7058100</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-20480079.69305337</t>
+          <t>-20401145.0830142</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-18278824.15793514</t>
+          <t>-19967004.72779879</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>211636508.0</t>
+          <t>204926741.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>44.40</t>
+          <t>46.21</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3406.004</t>
+          <t>5284.456</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.48</v>
+        <v>0.82</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>39.42</v>
+        <v>39.47</v>
       </c>
       <c r="AN26" t="n">
-        <v>39.93</v>
+        <v>39.91</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>59.36</t>
+          <t>82.20</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-103.83</t>
+          <t>-103.18</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>134570089.0</t>
+          <t>211636508.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>290045283.6</v>
+        <v>289039877.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>255657678.6</t>
+          <t>257985613.2</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>385379226.36</v>
+        <v>380318818.8</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>34387605</t>
+          <t>31054264</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-20880307.97216577</t>
+          <t>-20480079.69305337</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-15933226.08820361</t>
+          <t>-18278824.15793514</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>134570089.0</t>
+          <t>211636508.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>44.40</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4714.532</t>
+          <t>3406.004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>75.86</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>64.76</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-0.83</v>
+        <v>0.73</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.78</v>
+        <v>0.48</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>39.68000000000001</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>39.37</v>
+        <v>39.42</v>
       </c>
       <c r="AN27" t="n">
-        <v>39.96</v>
+        <v>39.93</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>59.36</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-104.40</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>186082304.0</t>
+          <t>134570089.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>330148862.4</v>
+        <v>290045283.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>277784390.5</t>
+          <t>255657678.6</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>391369102.88</v>
+        <v>385379226.36</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>52364471</t>
+          <t>34387605</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-21779777.40561344</t>
+          <t>-20880307.97216577</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-3756211.592579842</t>
+          <t>-15933226.08820361</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>186082304.0</t>
+          <t>134570089.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>44.04</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
+          <t>39.45</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>39.95</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
           <t>39.9</t>
-        </is>
-      </c>
-      <c r="CE27" t="inlineStr">
-        <is>
-          <t>40.05</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="CG27" t="inlineStr">
-        <is>
-          <t>39.35</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>14517.521</t>
+          <t>4714.532</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>80.49</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>68.29</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.33</v>
+        <v>-0.83</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.68000000000001</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>39.42</v>
+        <v>39.37</v>
       </c>
       <c r="AN28" t="n">
-        <v>39.99</v>
+        <v>39.96</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>50.22</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AQ28" t="n">
         <v>-0.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>592659518.0</t>
+          <t>186082304.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>330059250.6</v>
+        <v>330148862.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>291210114.1</t>
+          <t>277784390.5</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>402478507.04</v>
+        <v>391369102.88</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>38849136</t>
+          <t>52364471</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-25056789.37161956</t>
+          <t>-21779777.40561344</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>8254507.922331929</t>
+          <t>-3756211.592579842</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>592659518.0</t>
+          <t>186082304.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,22 +12165,22 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8001.481</t>
+          <t>14517.521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,12 +12408,12 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -12423,51 +12423,51 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>68.29</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>0.76</v>
+        <v>0.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>39.38</v>
+        <v>39.42</v>
       </c>
       <c r="AN29" t="n">
-        <v>40.02</v>
+        <v>39.99</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.27</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>50.22</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>320250967.0</t>
+          <t>592659518.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>251858830.2</v>
+        <v>330059250.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>253830312.9</t>
+          <t>291210114.1</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>402572081.14</v>
+        <v>402478507.04</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-1971482</t>
+          <t>38849136</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-31113388.87961073</t>
+          <t>-25056789.37161956</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-18443969.5535917</t>
+          <t>8254507.922331929</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>320250967.0</t>
+          <t>592659518.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,17 +12652,17 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
@@ -12689,7 +12689,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5475.163</t>
+          <t>8001.481</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>80.49</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>-0.61</v>
+        <v>0.76</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.11</v>
+        <v>0.42</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM30" t="n">
         <v>39.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>40.07</v>
+        <v>40.02</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>216663540.0</t>
+          <t>320250967.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>226931349.2</v>
+        <v>251858830.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>252085881.0</t>
+          <t>253830312.9</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>403055695.96</v>
+        <v>402572081.14</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-25154531</t>
+          <t>-1971482</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-33416919.66615964</t>
+          <t>-31113388.87961073</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-26739307.99942577</t>
+          <t>-18443969.5535917</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>216663540.0</t>
+          <t>320250967.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,22 +13009,22 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13074,14 +13074,14 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="CE30" t="inlineStr">
+        <is>
           <t>40.5</t>
         </is>
       </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
       <c r="CF30" t="inlineStr">
         <is>
           <t>39.1</t>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8360.012</t>
+          <t>5475.163</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>2.37</v>
+        <v>-0.61</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>39.32000000000001</t>
+          <t>39.34</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>39.45</v>
+        <v>39.38</v>
       </c>
       <c r="AN31" t="n">
-        <v>40.13</v>
+        <v>40.07</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-106.28</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>221270073.6</v>
+        <v>226931349.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>283648466.2</t>
+          <t>252085881.0</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>409053915.06</v>
+        <v>403055695.96</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-62378392</t>
+          <t>-25154531</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-34631030.87829307</t>
+          <t>-33416919.66615964</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-26536163.31492347</t>
+          <t>-26739307.99942577</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13431,22 +13431,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13533,7 +13533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4713.942</t>
+          <t>8360.012</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
           <t>71.05</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
       <c r="AH32" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="AI32" t="n">
-        <v>-1.45</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>39.48</v>
+        <v>39.45</v>
       </c>
       <c r="AN32" t="n">
-        <v>40.15</v>
+        <v>40.13</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.28</v>
+        <v>-0.18</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-106.75</t>
+          <t>-106.28</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>225419918.6</v>
+        <v>221270073.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>274182342.8</t>
+          <t>283648466.2</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>413674654.36</v>
+        <v>409053915.06</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-48762424</t>
+          <t>-62378392</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-36102824.98072391</t>
+          <t>-34631030.87829307</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-37986569.68295866</t>
+          <t>-26536163.31492347</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13853,22 +13853,22 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5128.692</t>
+          <t>4713.942</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,29 +14096,29 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>-0.05</v>
+        <v>1.64</v>
       </c>
       <c r="AI33" t="n">
-        <v>-1.3</v>
+        <v>-1.45</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -14127,32 +14127,32 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>39.53</v>
+        <v>39.48</v>
       </c>
       <c r="AN33" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.33</v>
+        <v>-0.28</v>
       </c>
       <c r="AR33" t="n">
         <v>-0.28</v>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-106.73</t>
+          <t>-106.75</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>252360977.6</v>
+        <v>225419918.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>282417854.9</t>
+          <t>274182342.8</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>423553251.3</v>
+        <v>413674654.36</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-30056877</t>
+          <t>-48762424</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-35760325.94395395</t>
+          <t>-36102824.98072391</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-36974729.3629033</t>
+          <t>-37986569.68295866</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>-0.61</v>
+        <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>-1.68</v>
+        <v>-1.3</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>39.71</v>
+        <v>39.53</v>
       </c>
       <c r="AN34" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ34" t="n">
         <v>-0.33</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>211062289.6716102</t>
+          <t>211151435.1029619</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>255801795.6</v>
+        <v>252360977.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>457544220.78</v>
+        <v>423553251.3</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,12 +14707,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2274.683</t>
+          <t>4731.625</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>58.37</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>48.73</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,70 +1144,70 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.38</v>
+        <v>-0.87</v>
       </c>
       <c r="AV2" t="n">
-        <v>24.93</v>
+        <v>20.95</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>115.9</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>92.78</v>
+        <v>95.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>75.31</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>13.86</v>
+        <v>13.54</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.85</v>
+        <v>12.19</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>609591487.8</v>
+        <v>532759803.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>631262663.6</t>
+          <t>644573649.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>192933562.72</v>
+        <v>203514658.18</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-21671175</t>
+          <t>-111813846</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>83050675.12229265</t>
+          <t>76417260.6081513</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>47092048.24731314</t>
+          <t>39933480.78037387</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>186.59</t>
+          <t>179.27</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4247.311</t>
+          <t>2274.683</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>62.52</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,75 +1631,75 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>97.28</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>94.43</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>26.38</v>
+        <v>24.93</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>89.89</v>
+        <v>92.78</v>
       </c>
       <c r="BA3" t="n">
-        <v>73.78</v>
+        <v>75.31</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>13.75</v>
+        <v>13.86</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.35</v>
+        <v>11.85</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>761248869</v>
+        <v>609591487.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>670874203.7</t>
+          <t>631262663.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>187661356.84</v>
+        <v>192933562.72</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>90374665</t>
+          <t>-21671175</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>89588607.28137983</t>
+          <t>83050675.12229265</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>84371258.084108</t>
+          <t>47092048.24731314</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>182.93</t>
+          <t>186.59</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5223.799</t>
+          <t>4247.311</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.44</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,75 +2118,75 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>97.28</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>95.34</t>
+          <t>94.43</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AV4" t="n">
-        <v>28.4</v>
+        <v>26.38</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>113.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>87.15000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="BA4" t="n">
-        <v>72.28</v>
+        <v>73.78</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>61.33</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>13.58</v>
+        <v>13.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.75</v>
+        <v>11.35</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>785663871.6</v>
+        <v>761248869</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>673850359.4</t>
+          <t>670874203.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>177872413.16</v>
+        <v>187661356.84</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>111813512</t>
+          <t>90374665</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>90537216.22633836</t>
+          <t>89588607.28137983</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>110442494.5622396</t>
+          <t>84371258.084108</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>178.05</t>
+          <t>182.93</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6754.556</t>
+          <t>5223.799</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>53.80</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,75 +2605,75 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.34</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>6.24</v>
+        <v>1.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>29.07</v>
+        <v>28.4</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>108.72</t>
+          <t>111.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>84.23999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>70.81999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.04</v>
+        <v>10.75</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>768544627.0</t>
+          <t>606949466.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>792585559.2</v>
+        <v>785663871.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>627953016.8</t>
+          <t>673850359.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>165738491.38</v>
+        <v>177872413.16</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>164632542</t>
+          <t>111813512</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>86918074.71071994</t>
+          <t>90537216.22633836</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>131259497.8323476</t>
+          <t>110442494.5622396</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>768544627.0</t>
+          <t>606949466.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>181.71</t>
+          <t>178.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8047.833</t>
+          <t>6754.556</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>61.13</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,75 +3092,75 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>95.88</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>8.449999999999999</v>
+        <v>6.24</v>
       </c>
       <c r="AV6" t="n">
-        <v>32.63</v>
+        <v>29.07</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>107.42</t>
+          <t>108.72</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>81</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>69.33</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.45</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>38.20</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>12.73</v>
+        <v>13.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.210000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-22.28</t>
+          <t>-17.63</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>917185834.0</t>
+          <t>768544627.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>756387495.4</v>
+        <v>792585559.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>559281476.7</t>
+          <t>627953016.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>150393261.88</v>
+        <v>165738491.38</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>197106018</t>
+          <t>164632542</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>78855997.77951492</t>
+          <t>86918074.71071994</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>138996467.4742038</t>
+          <t>131259497.8323476</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>917185834.0</t>
+          <t>768544627.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>184.15</t>
+          <t>181.71</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9709.495</t>
+          <t>8047.833</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>61.13</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,75 +3579,75 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>86.04</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>33.71</v>
+        <v>32.63</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>16.83</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>104.02</t>
+          <t>107.42</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>77.8</v>
+        <v>81</v>
       </c>
       <c r="BA7" t="n">
-        <v>67.81</v>
+        <v>69.33</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>38.20</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>11.64</v>
+        <v>12.73</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-24.43</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1023125243.0</t>
+          <t>917185834.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>652933839.4</v>
+        <v>756387495.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>490790050.9</t>
+          <t>559281476.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>132060883.02</v>
+        <v>150393261.88</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>162143788</t>
+          <t>197106018</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>67921366.92593512</t>
+          <t>78855997.77951492</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>129159278.0884913</t>
+          <t>138996467.4742038</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1023125243.0</t>
+          <t>917185834.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>158.54</t>
+          <t>184.15</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5847.669</t>
+          <t>9709.495</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>48.69</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.23</t>
+          <t>100.01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,75 +4066,75 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>91.35</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>86.04</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>6.16</v>
+        <v>1.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>34.58</v>
+        <v>33.71</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>101.26</t>
+          <t>104.02</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>75.23999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>66.5</v>
+        <v>67.81</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>11.15</v>
+        <v>11.64</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-36.68</t>
+          <t>-31.65</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>612514188.0</t>
+          <t>1023125243.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>580499538.4</v>
+        <v>652933839.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>394646540.2</t>
+          <t>490790050.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>111613087.96</v>
+        <v>132060883.02</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>185852998</t>
+          <t>162143788</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>56787201.26001582</t>
+          <t>67921366.92593512</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>99142668.07002717</t>
+          <t>129159278.0884913</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>612514188.0</t>
+          <t>1023125243.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>162.20</t>
+          <t>158.54</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6258.781</t>
+          <t>5847.669</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>63.76</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>60.23</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-10.60</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,75 +4553,75 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>71.09</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.45</v>
+        <v>6.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>34.47</v>
+        <v>34.58</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>101.26</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>72.62</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>65.17</v>
+        <v>66.5</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.71</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>48.59</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>10.21</v>
+        <v>11.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.59</v>
+        <v>7.5</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-44.37</t>
+          <t>-38.44</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>641557904.0</t>
+          <t>612514188.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>562036847.2</v>
+        <v>580499538.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>343214733.3</t>
+          <t>394646540.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>99368544.2</v>
+        <v>111613087.96</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>218822113</t>
+          <t>185852998</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>49086207.2945592</t>
+          <t>56787201.26001582</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>96715028.6482917</t>
+          <t>99142668.07002717</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>641557904.0</t>
+          <t>612514188.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>139.27</t>
+          <t>162.20</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5658.101</t>
+          <t>6258.781</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>56.45</t>
+          <t>63.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>58.28</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>-10.60</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,75 +5040,75 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.09</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>15.49</v>
+        <v>0.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>33.7</v>
+        <v>34.47</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>94.38000000000001</t>
+          <t>97.66</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>70.59</v>
+        <v>72.62</v>
       </c>
       <c r="BA10" t="n">
-        <v>64.03</v>
+        <v>65.17</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>9.82</v>
+        <v>10.21</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.69</v>
+        <v>6.59</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-52.00</t>
+          <t>-45.91</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,48 +5118,48 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>587554308.0</t>
+          <t>641557904.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>463320474.4</v>
+        <v>562036847.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>296148015.6</t>
+          <t>343214733.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>86557856.04000001</v>
+        <v>99368544.2</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>167172458</t>
+          <t>218822113</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>40426421.59388057</t>
+          <t>49086207.2945592</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>86681037.45123065</t>
+          <t>96715028.6482917</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>587554308.0</t>
+          <t>641557904.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>165.85</t>
+          <t>139.27</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4184.853</t>
+          <t>5658.101</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>56.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>50.76</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>43.10</t>
+          <t>58.28</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,56 +5546,56 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>13.79</v>
+        <v>15.49</v>
       </c>
       <c r="AV11" t="n">
-        <v>27.98</v>
+        <v>33.7</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>87.44000000000001</t>
+          <t>94.38000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>68.31999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="BA11" t="n">
-        <v>62.67</v>
+        <v>64.03</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>55.15</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>8.06</v>
+        <v>9.82</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.65</v>
+        <v>5.69</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-60.72</t>
+          <t>-53.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>21606123.69456067</t>
+          <t>22689598.61699164</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>399917554.0</t>
+          <t>587554308.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>362175458</v>
+        <v>463320474.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>241071010.7</t>
+          <t>296148015.6</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>74816561.88</v>
+        <v>86557856.04000001</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>121104447</t>
+          <t>167172458</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>32016491.43799874</t>
+          <t>40426421.59388057</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>75037112.5464567</t>
+          <t>86681037.45123065</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>399917554.0</t>
+          <t>587554308.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>142.68</t>
+          <t>165.85</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>132.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>784.817</t>
+          <t>809.469</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-2.41</v>
+        <v>-1.48</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>53.66</v>
+        <v>53.58</v>
       </c>
       <c r="BA12" t="n">
-        <v>55.83</v>
+        <v>55.68</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-111.39</t>
+          <t>-110.75</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>44882535.4</v>
+        <v>45663772.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>44153034.1</t>
+          <t>43887254.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>71382431.34</v>
+        <v>70595577.38</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>1776517</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-4457771.923717958</t>
+          <t>-4579632.064807353</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-5512115.378324404</t>
+          <t>-5249862.840799026</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>54.2</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>847.176</t>
+          <t>784.817</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.78</v>
+        <v>-2.41</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>53.68</v>
+        <v>53.66</v>
       </c>
       <c r="BA13" t="n">
-        <v>56</v>
+        <v>55.83</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-112.22</t>
+          <t>-111.39</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>43806952</v>
+        <v>44882535.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>47872049.3</t>
+          <t>44153034.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>71746544.26000001</v>
+        <v>71382431.34</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-4065097</t>
+          <t>729501</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-4266073.113789514</t>
+          <t>-4457771.923717958</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-5492034.846991934</t>
+          <t>-5512115.378324404</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>643.823</t>
+          <t>847.176</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-32.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>1.29</v>
+        <v>-0.78</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>53.67</v>
+        <v>53.68</v>
       </c>
       <c r="BA14" t="n">
-        <v>56.14</v>
+        <v>56</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>61.68</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.86</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-112.22</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>45837999.8</v>
+        <v>43806952</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>67426005.1</t>
+          <t>47872049.3</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>73613007.12</v>
+        <v>71746544.26000001</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-21588005</t>
+          <t>-4065097</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4043170.980479982</t>
+          <t>-4266073.113789514</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-5754998.914838694</t>
+          <t>-5492034.846991934</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1133.708</t>
+          <t>643.823</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.38</t>
+          <t>-32.02</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>53.81999999999999</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>53.5</v>
+        <v>53.67</v>
       </c>
       <c r="BA15" t="n">
-        <v>56.28</v>
+        <v>56.14</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>61.94</t>
+          <t>61.68</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.63</v>
+        <v>-0.51</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-115.04</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>62174644.0</t>
+          <t>35278757.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>46682300.4</v>
+        <v>45837999.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>69037086.7</t>
+          <t>67426005.1</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>76055049.48</v>
+        <v>73613007.12</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-22354786</t>
+          <t>-21588005</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-3731929.537869307</t>
+          <t>-4043170.980479982</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-4771985.336232685</t>
+          <t>-5754998.914838694</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>62174644.0</t>
+          <t>35278757.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-19.86</t>
+          <t>-20.58</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
           <t>54.4</t>
         </is>
       </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>732.949</t>
+          <t>1133.708</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-32.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-26.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.04</v>
+        <v>2.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>53.81999999999999</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>56.46</v>
+        <v>56.28</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>62.18</t>
+          <t>61.94</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.83</v>
+        <v>-0.63</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-115.04</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>39429216.0</t>
+          <t>62174644.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>42110736.8</v>
+        <v>46682300.4</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>71945346.8</t>
+          <t>69037086.7</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>77478822.28</v>
+        <v>76055049.48</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-29834610</t>
+          <t>-22354786</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-3542828.48362142</t>
+          <t>-3731929.537869307</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-6078954.354787223</t>
+          <t>-4771985.336232685</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>39429216.0</t>
+          <t>62174644.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-19.86</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>680.718</t>
+          <t>732.949</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-39.40</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.38</v>
+        <v>-0.04</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>53.16</v>
+        <v>53.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>56.69</v>
+        <v>56.46</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>62.47</t>
+          <t>62.18</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.24</v>
+        <v>-1.16</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-117.70</t>
+          <t>-116.54</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>36110738.0</t>
+          <t>39429216.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>43423532.8</v>
+        <v>42110736.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>71651185.7</t>
+          <t>71945346.8</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>79714884.08</v>
+        <v>77478822.28</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-28227652</t>
+          <t>-29834610</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-3081714.688864001</t>
+          <t>-3542828.48362142</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-5291937.297194161</t>
+          <t>-6078954.354787223</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>36110738.0</t>
+          <t>39429216.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,14 +8638,14 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
       <c r="CH17" t="inlineStr">
         <is>
           <t>4.52</t>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1033.31</t>
+          <t>680.718</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-39.40</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-30.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.37</v>
+        <v>-1.38</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.54</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.18</v>
+        <v>53.16</v>
       </c>
       <c r="BA18" t="n">
-        <v>56.96</v>
+        <v>56.69</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>62.47</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-118.92</t>
+          <t>-117.70</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>56196644.0</t>
+          <t>36110738.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>51937146.6</v>
+        <v>43423532.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>71761786.4</t>
+          <t>71651185.7</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>82129229.45999999</v>
+        <v>79714884.08</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-19824639</t>
+          <t>-28227652</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2679856.032803972</t>
+          <t>-3081714.688864001</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-3623078.240018561</t>
+          <t>-5291937.297194161</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>56196644.0</t>
+          <t>36110738.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-21.74</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>741.339</t>
+          <t>1033.31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.46</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.71</v>
+        <v>0.37</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>53.78000000000001</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.06</v>
+        <v>53.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>57.19</v>
+        <v>56.96</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.99</v>
+        <v>-0.89</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.43</v>
+        <v>-1.32</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-118.92</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>39500260.0</t>
+          <t>56196644.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>89014010.40000001</v>
+        <v>51937146.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>68869337.4</t>
+          <t>71761786.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>85661512.38</v>
+        <v>82129229.45999999</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>20144673</t>
+          <t>-19824639</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-2508361.086037683</t>
+          <t>-2679856.032803972</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-3261659.578338452</t>
+          <t>-3623078.240018561</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>39500260.0</t>
+          <t>56196644.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-21.74</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
           <t>54.0</t>
-        </is>
-      </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>53.4</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>734.995</t>
+          <t>741.339</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34.60</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-28.27</t>
+          <t>-29.46</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>61.83</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.78</v>
+        <v>-0.71</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-9.23</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>53.78000000000001</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>52.97</v>
+        <v>53.06</v>
       </c>
       <c r="BA20" t="n">
-        <v>57.48</v>
+        <v>57.19</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>63.32</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-1.04</v>
+        <v>-0.99</v>
       </c>
       <c r="BE20" t="n">
-        <v>-1.54</v>
+        <v>-1.43</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-122.03</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>39316826.0</t>
+          <t>39500260.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>91391873</v>
+        <v>89014010.40000001</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>67899796.5</t>
+          <t>68869337.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>88385240.08</v>
+        <v>85661512.38</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>23492076</t>
+          <t>20144673</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-2371397.72380118</t>
+          <t>-2508361.086037683</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-839961.0767119527</t>
+          <t>-3261659.578338452</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>39316826.0</t>
+          <t>39500260.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-21.30</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>54.6</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>854.825</t>
+          <t>734.995</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>34.60</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-29.72</t>
+          <t>-28.27</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>809</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>80.95</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>56.06</t>
+          <t>61.83</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.41</v>
+        <v>0.78</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-9.17</t>
+          <t>-9.23</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>52.98</v>
+        <v>52.97</v>
       </c>
       <c r="BA21" t="n">
-        <v>57.76</v>
+        <v>57.48</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>63.59</t>
+          <t>63.32</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>28.70</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-1.19</v>
+        <v>-1.04</v>
       </c>
       <c r="BE21" t="n">
-        <v>-1.67</v>
+        <v>-1.54</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-123.80</t>
+          <t>-122.03</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>492304940.2520834</t>
+          <t>491712288.6054091</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>45993196.0</t>
+          <t>39316826.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>101779956.8</v>
+        <v>91391873</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>68158526.5</t>
+          <t>67899796.5</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>90493244.14</v>
+        <v>88385240.08</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>33621430</t>
+          <t>23492076</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-2649840.750544676</t>
+          <t>-2371397.72380118</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>2669260.464065641</t>
+          <t>-839961.0767119527</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>45993196.0</t>
+          <t>39316826.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-21.30</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4167.968</t>
+          <t>8066.275</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,87 +10863,87 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-1.45</v>
+        <v>0.05</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>39.98</v>
+        <v>40.02</v>
       </c>
       <c r="BA22" t="n">
-        <v>39.74</v>
+        <v>39.77</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>129.54</t>
+          <t>108.24</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>467047398.4</v>
+        <v>469787958.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>346645174.9</t>
+          <t>345844403.0</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>361420707.74</v>
+        <v>364415966.86</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>120402223</t>
+          <t>123943555</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>11297179.36056474</t>
+          <t>11702769.29568647</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>19249505.79997534</t>
+          <t>13933513.93885595</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10398.551</t>
+          <t>4167.968</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>62.16</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.37</v>
+        <v>-1.45</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>39.95</v>
+        <v>39.98</v>
       </c>
       <c r="BA23" t="n">
-        <v>39.71</v>
+        <v>39.74</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>261.75</t>
+          <t>129.54</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-98.51</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>455929202</v>
+        <v>467047398.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>394210697.6</t>
+          <t>346645174.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>365467847.18</v>
+        <v>361420707.74</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>61718504</t>
+          <t>120402223</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>9851301.826126453</t>
+          <t>11297179.36056474</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>43839053.96586108</t>
+          <t>19249505.79997534</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17316.689</t>
+          <t>10398.551</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.16</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>5.03</v>
+        <v>0.37</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.18</v>
+        <v>1.14</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>39.87</v>
+        <v>39.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>39.7</v>
+        <v>39.71</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>845.58</t>
+          <t>261.75</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-98.51</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>415088503.4</v>
+        <v>455929202</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>369426821.9</t>
+          <t>394210697.6</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>365490619.66</v>
+        <v>365467847.18</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>45661681</t>
+          <t>61718504</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>3671710.527992884</t>
+          <t>9851301.826126453</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>49293584.23977429</t>
+          <t>43839053.96586108</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16723.374</t>
+          <t>17316.689</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12324,33 +12324,33 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>4.78</v>
+        <v>5.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.98</v>
+        <v>0.18</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>39.71</v>
+        <v>39.87</v>
       </c>
       <c r="BA25" t="n">
-        <v>39.68</v>
+        <v>39.7</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>845.58</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-100.57</t>
+          <t>-99.48</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>691584961.0</t>
+          <t>724944050.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>324711741.2</v>
+        <v>415088503.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>317425091.0</t>
+          <t>369426821.9</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>358185679.98</v>
+        <v>365490619.66</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>7286650</t>
+          <t>45661681</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-4623175.601421917</t>
+          <t>3671710.527992884</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>23797318.1225155</t>
+          <t>49293584.23977429</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>691584961.0</t>
+          <t>724944050.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>41.95</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>41.2</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8072.809</t>
+          <t>16723.374</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>62.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>2.51</v>
+        <v>4.78</v>
       </c>
       <c r="AV26" t="n">
-        <v>-1.34</v>
+        <v>-0.98</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>39.07000000000001</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>39.6</v>
+        <v>39.71</v>
       </c>
       <c r="BA26" t="n">
-        <v>39.7</v>
+        <v>39.68</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-221.25</t>
+          <t>216.96</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-100.89</t>
+          <t>-100.57</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>319680608.0</t>
+          <t>691584961.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>221900847.4</v>
+        <v>324711741.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>269430245.7</t>
+          <t>317425091.0</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>352970456.12</v>
+        <v>358185679.98</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-47529398</t>
+          <t>7286650</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-9790538.096683266</t>
+          <t>-4623175.601421917</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-9901635.299372643</t>
+          <t>23797318.1225155</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>319680608.0</t>
+          <t>691584961.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2949.722</t>
+          <t>8072.809</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,33 +13319,33 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>62.07</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-2.15</v>
+        <v>2.51</v>
       </c>
       <c r="AV27" t="n">
-        <v>-1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -13355,30 +13355,30 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>39.07000000000001</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>39.51</v>
+        <v>39.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>39.72</v>
+        <v>39.7</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-1023.06</t>
+          <t>-221.25</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-100.40</t>
+          <t>-100.89</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>112753367.0</t>
+          <t>319680608.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>226242951.4</v>
+        <v>221900847.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>250919193.8</t>
+          <t>269430245.7</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>352572412.46</v>
+        <v>352970456.12</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-24676242</t>
+          <t>-47529398</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-9770338.605285197</t>
+          <t>-9790538.096683266</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-17842472.53423518</t>
+          <t>-9901635.299372643</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>112753367.0</t>
+          <t>319680608.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5880.808</t>
+          <t>2949.722</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-3.58</v>
+        <v>-2.15</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.18</v>
+        <v>-1.06</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>39.6</v>
+        <v>39.51</v>
       </c>
       <c r="BA28" t="n">
-        <v>39.79</v>
+        <v>39.72</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-418.73</t>
+          <t>-1023.06</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-99.38</t>
+          <t>-100.40</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>226479531.0</t>
+          <t>112753367.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>332492193.2</v>
+        <v>226242951.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>258252087.5</t>
+          <t>250919193.8</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>367586169.62</v>
+        <v>352572412.46</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>74240105</t>
+          <t>-24676242</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-8302677.890930655</t>
+          <t>-9770338.605285197</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-6378518.743530452</t>
+          <t>-17842472.53423518</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>226479531.0</t>
+          <t>112753367.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,17 +14050,17 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6994.968</t>
+          <t>5880.808</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,149 +14112,149 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>28.75</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>38.55</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>2025/04/09</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
           <t>38.85</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>2025/04/09</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
       <c r="AI29" t="inlineStr">
         <is>
           <t>2025/11/21</t>
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14308,51 +14308,51 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>-3.02</v>
+        <v>-3.58</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>39.64</v>
+        <v>39.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>39.86</v>
+        <v>39.79</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-418.73</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-98.74</t>
+          <t>-99.38</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>273060239.0</t>
+          <t>226479531.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>323765140.4</v>
+        <v>332492193.2</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>294870086.2</t>
+          <t>258252087.5</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>374398444.12</v>
+        <v>367586169.62</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>28895054</t>
+          <t>74240105</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-8652525.008639783</t>
+          <t>-8302677.890930655</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-1958583.801683307</t>
+          <t>-6378518.743530452</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>273060239.0</t>
+          <t>226479531.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4472.26</t>
+          <t>6994.968</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,63 +14780,63 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>-1.09</v>
+        <v>-3.02</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.81</v>
+        <v>1.05</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>39.67</v>
+        <v>39.64</v>
       </c>
       <c r="BA30" t="n">
-        <v>39.89</v>
+        <v>39.86</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>199.33</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="BE30" t="n">
         <v>0.05</v>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-98.73</t>
+          <t>-98.74</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>177530492.0</t>
+          <t>273060239.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>310138440.8</v>
+        <v>323765140.4</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>299589159.0</t>
+          <t>294870086.2</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>378030653.4</v>
+        <v>374398444.12</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>10549281</t>
+          <t>28895054</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-9869605.228086414</t>
+          <t>-8652525.008639783</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-565231.7489843965</t>
+          <t>-1958583.801683307</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>177530492.0</t>
+          <t>273060239.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8388.781</t>
+          <t>4472.26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,66 +15267,66 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>-0.62</v>
+        <v>-1.09</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>39.65</v>
+        <v>39.67</v>
       </c>
       <c r="BA31" t="n">
-        <v>39.91</v>
+        <v>39.89</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>575.93</t>
+          <t>199.33</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-99.36</t>
+          <t>-98.73</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>216488950.6604167</t>
+          <t>216882274.0485437</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>341391128.0</t>
+          <t>177530492.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>316959644</v>
+        <v>310138440.8</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>303502463.8</t>
+          <t>299589159.0</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>382616367.06</v>
+        <v>378030653.4</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>13457180</t>
+          <t>10549281</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-11561309.49701405</t>
+          <t>-9869605.228086414</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>11680788.06733489</t>
+          <t>-565231.7489843965</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>341391128.0</t>
+          <t>177530492.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>52.77</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4731.625</t>
+          <t>3681.336</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-26.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,70 +1144,70 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.87</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>20.95</v>
+        <v>16.23</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>95.5</v>
+        <v>97.39</v>
       </c>
       <c r="BA2" t="n">
-        <v>76.70999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>64.04</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>13.54</v>
+        <v>12.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>532759803.4</v>
+        <v>457066679.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>644573649.4</t>
+          <t>624826119.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>203514658.18</v>
+        <v>211265158</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-111813846</t>
+          <t>-167759440</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>76417260.6081513</t>
+          <t>68230453.75828296</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>39933480.78037387</t>
+          <t>23203016.08400708</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>179.27</t>
+          <t>153.66</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2274.683</t>
+          <t>4731.625</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-10.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>58.37</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>48.73</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,75 +1631,75 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.38</v>
+        <v>-0.87</v>
       </c>
       <c r="AV3" t="n">
-        <v>24.93</v>
+        <v>20.95</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>115.9</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>92.78</v>
+        <v>95.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>75.31</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>13.86</v>
+        <v>13.54</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.85</v>
+        <v>12.19</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>609591487.8</v>
+        <v>532759803.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>631262663.6</t>
+          <t>644573649.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>192933562.72</v>
+        <v>203514658.18</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-21671175</t>
+          <t>-111813846</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>83050675.12229265</t>
+          <t>76417260.6081513</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>47092048.24731314</t>
+          <t>39933480.78037387</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>186.59</t>
+          <t>179.27</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4247.311</t>
+          <t>2274.683</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>62.52</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,75 +2118,75 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>97.28</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>94.43</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>26.38</v>
+        <v>24.93</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>89.89</v>
+        <v>92.78</v>
       </c>
       <c r="BA4" t="n">
-        <v>73.78</v>
+        <v>75.31</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>13.75</v>
+        <v>13.86</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.35</v>
+        <v>11.85</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>761248869</v>
+        <v>609591487.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>670874203.7</t>
+          <t>631262663.6</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>187661356.84</v>
+        <v>192933562.72</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>90374665</t>
+          <t>-21671175</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>89588607.28137983</t>
+          <t>83050675.12229265</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>84371258.084108</t>
+          <t>47092048.24731314</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>182.93</t>
+          <t>186.59</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5223.799</t>
+          <t>4247.311</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.44</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,75 +2605,75 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>97.28</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>95.34</t>
+          <t>94.43</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AV5" t="n">
-        <v>28.4</v>
+        <v>26.38</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>113.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>87.15000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="BA5" t="n">
-        <v>72.28</v>
+        <v>73.78</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>61.33</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>13.58</v>
+        <v>13.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.75</v>
+        <v>11.35</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>785663871.6</v>
+        <v>761248869</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>673850359.4</t>
+          <t>670874203.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>177872413.16</v>
+        <v>187661356.84</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>111813512</t>
+          <t>90374665</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>90537216.22633836</t>
+          <t>89588607.28137983</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>110442494.5622396</t>
+          <t>84371258.084108</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>178.05</t>
+          <t>182.93</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6754.556</t>
+          <t>5223.799</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>53.80</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,75 +3092,75 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.34</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>6.24</v>
+        <v>1.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>29.07</v>
+        <v>28.4</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>108.72</t>
+          <t>111.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>84.23999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>70.81999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.04</v>
+        <v>10.75</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-17.63</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>768544627.0</t>
+          <t>606949466.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>792585559.2</v>
+        <v>785663871.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>627953016.8</t>
+          <t>673850359.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>165738491.38</v>
+        <v>177872413.16</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>164632542</t>
+          <t>111813512</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>86918074.71071994</t>
+          <t>90537216.22633836</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>131259497.8323476</t>
+          <t>110442494.5622396</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>768544627.0</t>
+          <t>606949466.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>181.71</t>
+          <t>178.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8047.833</t>
+          <t>6754.556</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>61.13</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,75 +3579,75 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>95.88</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>8.449999999999999</v>
+        <v>6.24</v>
       </c>
       <c r="AV7" t="n">
-        <v>32.63</v>
+        <v>29.07</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>107.42</t>
+          <t>108.72</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>81</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>69.33</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.45</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>38.20</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>12.73</v>
+        <v>13.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.210000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-24.43</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>917185834.0</t>
+          <t>768544627.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>756387495.4</v>
+        <v>792585559.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>559281476.7</t>
+          <t>627953016.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>150393261.88</v>
+        <v>165738491.38</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>197106018</t>
+          <t>164632542</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>78855997.77951492</t>
+          <t>86918074.71071994</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>138996467.4742038</t>
+          <t>131259497.8323476</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>917185834.0</t>
+          <t>768544627.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>184.15</t>
+          <t>181.71</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9709.495</t>
+          <t>8047.833</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>61.13</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,75 +4066,75 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>86.04</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>33.71</v>
+        <v>32.63</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>16.83</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>104.02</t>
+          <t>107.42</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>77.8</v>
+        <v>81</v>
       </c>
       <c r="BA8" t="n">
-        <v>67.81</v>
+        <v>69.33</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>38.20</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>11.64</v>
+        <v>12.73</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-31.65</t>
+          <t>-24.57</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1023125243.0</t>
+          <t>917185834.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>652933839.4</v>
+        <v>756387495.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>490790050.9</t>
+          <t>559281476.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>132060883.02</v>
+        <v>150393261.88</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>162143788</t>
+          <t>197106018</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>67921366.92593512</t>
+          <t>78855997.77951492</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>129159278.0884913</t>
+          <t>138996467.4742038</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1023125243.0</t>
+          <t>917185834.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>158.54</t>
+          <t>184.15</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5847.669</t>
+          <t>9709.495</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>48.69</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.23</t>
+          <t>100.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,75 +4553,75 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>91.35</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>86.04</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>6.16</v>
+        <v>1.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>34.58</v>
+        <v>33.71</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>101.26</t>
+          <t>104.02</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>75.23999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>66.5</v>
+        <v>67.81</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>11.15</v>
+        <v>11.64</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-38.44</t>
+          <t>-31.77</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>612514188.0</t>
+          <t>1023125243.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>580499538.4</v>
+        <v>652933839.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>394646540.2</t>
+          <t>490790050.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>111613087.96</v>
+        <v>132060883.02</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>185852998</t>
+          <t>162143788</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>56787201.26001582</t>
+          <t>67921366.92593512</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>99142668.07002717</t>
+          <t>129159278.0884913</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>612514188.0</t>
+          <t>1023125243.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>162.20</t>
+          <t>158.54</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6258.781</t>
+          <t>5847.669</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>63.76</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>60.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-10.60</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,75 +5040,75 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>71.09</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.45</v>
+        <v>6.16</v>
       </c>
       <c r="AV10" t="n">
-        <v>34.47</v>
+        <v>34.58</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>101.26</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>72.62</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="BA10" t="n">
-        <v>65.17</v>
+        <v>66.5</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>56.71</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>48.59</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>10.21</v>
+        <v>11.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.59</v>
+        <v>7.5</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-45.91</t>
+          <t>-38.55</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,48 +5118,48 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>641557904.0</t>
+          <t>612514188.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>562036847.2</v>
+        <v>580499538.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>343214733.3</t>
+          <t>394646540.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>99368544.2</v>
+        <v>111613087.96</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>218822113</t>
+          <t>185852998</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>49086207.2945592</t>
+          <t>56787201.26001582</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>96715028.6482917</t>
+          <t>99142668.07002717</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>641557904.0</t>
+          <t>612514188.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>139.27</t>
+          <t>162.20</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5658.101</t>
+          <t>6258.781</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>56.45</t>
+          <t>63.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.28</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>-10.60</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,75 +5527,75 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.09</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>15.49</v>
+        <v>0.45</v>
       </c>
       <c r="AV11" t="n">
-        <v>33.7</v>
+        <v>34.47</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>94.38000000000001</t>
+          <t>97.66</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>70.59</v>
+        <v>72.62</v>
       </c>
       <c r="BA11" t="n">
-        <v>64.03</v>
+        <v>65.17</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>55.87</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>9.82</v>
+        <v>10.21</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.69</v>
+        <v>6.59</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-53.33</t>
+          <t>-46.01</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>22689598.61699164</t>
+          <t>23471836.32267037</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>587554308.0</t>
+          <t>641557904.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>463320474.4</v>
+        <v>562036847.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>296148015.6</t>
+          <t>343214733.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>86557856.04000001</v>
+        <v>99368544.2</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>167172458</t>
+          <t>218822113</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>40426421.59388057</t>
+          <t>49086207.2945592</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>86681037.45123065</t>
+          <t>96715028.6482917</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>587554308.0</t>
+          <t>641557904.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>165.85</t>
+          <t>139.27</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>116.85</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>809.469</t>
+          <t>1007.736</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.48</v>
+        <v>-1.27</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.59</v>
+        <v>-0.34</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>53.58</v>
+        <v>53.56</v>
       </c>
       <c r="BA12" t="n">
-        <v>55.68</v>
+        <v>55.53</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.57</v>
+        <v>-0.61</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-110.75</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>45663772.6</v>
+        <v>43773654.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>43887254.7</t>
+          <t>45227977.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>70595577.38</v>
+        <v>69838946.16</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>1776517</t>
+          <t>-1454322</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-4579632.064807353</t>
+          <t>-4525979.519223342</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-5249862.840799026</t>
+          <t>-4230890.51851128</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>784.817</t>
+          <t>809.469</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-2.41</v>
+        <v>-1.48</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>53.66</v>
+        <v>53.58</v>
       </c>
       <c r="BA13" t="n">
-        <v>55.83</v>
+        <v>55.68</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-111.39</t>
+          <t>-110.75</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>44882535.4</v>
+        <v>45663772.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>44153034.1</t>
+          <t>43887254.7</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>71382431.34</v>
+        <v>70595577.38</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>1776517</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-4457771.923717958</t>
+          <t>-4579632.064807353</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-5512115.378324404</t>
+          <t>-5249862.840799026</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>54.2</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>847.176</t>
+          <t>784.817</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.78</v>
+        <v>-2.41</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>53.68</v>
+        <v>53.66</v>
       </c>
       <c r="BA14" t="n">
-        <v>56</v>
+        <v>55.83</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-112.22</t>
+          <t>-111.39</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>43806952</v>
+        <v>44882535.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>47872049.3</t>
+          <t>44153034.1</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>71746544.26000001</v>
+        <v>71382431.34</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4065097</t>
+          <t>729501</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4266073.113789514</t>
+          <t>-4457771.923717958</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-5492034.846991934</t>
+          <t>-5512115.378324404</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>643.823</t>
+          <t>847.176</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.29</v>
+        <v>-0.78</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>53.67</v>
+        <v>53.68</v>
       </c>
       <c r="BA15" t="n">
-        <v>56.14</v>
+        <v>56</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>61.68</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.86</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-112.22</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>45837999.8</v>
+        <v>43806952</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>67426005.1</t>
+          <t>47872049.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>73613007.12</v>
+        <v>71746544.26000001</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-21588005</t>
+          <t>-4065097</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-4043170.980479982</t>
+          <t>-4266073.113789514</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-5754998.914838694</t>
+          <t>-5492034.846991934</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1133.708</t>
+          <t>643.823</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-32.38</t>
+          <t>-32.02</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>53.81999999999999</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>53.5</v>
+        <v>53.67</v>
       </c>
       <c r="BA16" t="n">
-        <v>56.28</v>
+        <v>56.14</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>61.94</t>
+          <t>61.68</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.63</v>
+        <v>-0.51</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-115.04</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>62174644.0</t>
+          <t>35278757.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>46682300.4</v>
+        <v>45837999.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>69037086.7</t>
+          <t>67426005.1</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>76055049.48</v>
+        <v>73613007.12</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-22354786</t>
+          <t>-21588005</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-3731929.537869307</t>
+          <t>-4043170.980479982</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-4771985.336232685</t>
+          <t>-5754998.914838694</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>62174644.0</t>
+          <t>35278757.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-19.86</t>
+          <t>-20.58</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
           <t>54.4</t>
         </is>
       </c>
-      <c r="CR16" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>732.949</t>
+          <t>1133.708</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-32.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-26.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.04</v>
+        <v>2.75</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>53.81999999999999</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>56.46</v>
+        <v>56.28</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>62.18</t>
+          <t>61.94</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.83</v>
+        <v>-0.63</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-115.04</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>39429216.0</t>
+          <t>62174644.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>42110736.8</v>
+        <v>46682300.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>71945346.8</t>
+          <t>69037086.7</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>77478822.28</v>
+        <v>76055049.48</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-29834610</t>
+          <t>-22354786</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-3542828.48362142</t>
+          <t>-3731929.537869307</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-6078954.354787223</t>
+          <t>-4771985.336232685</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>39429216.0</t>
+          <t>62174644.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-19.86</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>680.718</t>
+          <t>732.949</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-39.40</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.38</v>
+        <v>-0.04</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.6</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.16</v>
+        <v>53.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>56.69</v>
+        <v>56.46</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>62.47</t>
+          <t>62.18</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.24</v>
+        <v>-1.16</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-117.70</t>
+          <t>-116.54</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>36110738.0</t>
+          <t>39429216.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>43423532.8</v>
+        <v>42110736.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>71651185.7</t>
+          <t>71945346.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>79714884.08</v>
+        <v>77478822.28</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-28227652</t>
+          <t>-29834610</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-3081714.688864001</t>
+          <t>-3542828.48362142</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-5291937.297194161</t>
+          <t>-6078954.354787223</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>36110738.0</t>
+          <t>39429216.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1033.31</t>
+          <t>680.718</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-39.40</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-30.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.37</v>
+        <v>-1.38</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.54</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.18</v>
+        <v>53.16</v>
       </c>
       <c r="BA19" t="n">
-        <v>56.96</v>
+        <v>56.69</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>62.47</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-118.92</t>
+          <t>-117.70</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>56196644.0</t>
+          <t>36110738.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>51937146.6</v>
+        <v>43423532.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>71761786.4</t>
+          <t>71651185.7</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>82129229.45999999</v>
+        <v>79714884.08</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-19824639</t>
+          <t>-28227652</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-2679856.032803972</t>
+          <t>-3081714.688864001</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-3623078.240018561</t>
+          <t>-5291937.297194161</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>56196644.0</t>
+          <t>36110738.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-21.74</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>741.339</t>
+          <t>1033.31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-29.46</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.71</v>
+        <v>0.37</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>53.78000000000001</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>53.06</v>
+        <v>53.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>57.19</v>
+        <v>56.96</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.99</v>
+        <v>-0.89</v>
       </c>
       <c r="BE20" t="n">
-        <v>-1.43</v>
+        <v>-1.32</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-118.92</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>39500260.0</t>
+          <t>56196644.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>89014010.40000001</v>
+        <v>51937146.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>68869337.4</t>
+          <t>71761786.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>85661512.38</v>
+        <v>82129229.45999999</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>20144673</t>
+          <t>-19824639</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-2508361.086037683</t>
+          <t>-2679856.032803972</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-3261659.578338452</t>
+          <t>-3623078.240018561</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>39500260.0</t>
+          <t>56196644.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-21.74</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,14 +10099,14 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
           <t>2.27</t>
         </is>
       </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
       <c r="CH20" t="inlineStr">
         <is>
           <t>4.52</t>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
           <t>54.0</t>
-        </is>
-      </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="CT20" t="inlineStr">
-        <is>
-          <t>53.4</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>734.995</t>
+          <t>741.339</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>34.60</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-28.27</t>
+          <t>-29.46</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>61.83</t>
+          <t>50.29</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.78</v>
+        <v>-0.71</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-9.23</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>53.78000000000001</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>52.97</v>
+        <v>53.06</v>
       </c>
       <c r="BA21" t="n">
-        <v>57.48</v>
+        <v>57.19</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>63.32</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-1.04</v>
+        <v>-0.99</v>
       </c>
       <c r="BE21" t="n">
-        <v>-1.54</v>
+        <v>-1.43</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-122.03</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>491712288.6054091</t>
+          <t>491140784.16482</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>39316826.0</t>
+          <t>39500260.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>91391873</v>
+        <v>89014010.40000001</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>67899796.5</t>
+          <t>68869337.4</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>88385240.08</v>
+        <v>85661512.38</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>23492076</t>
+          <t>20144673</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-2371397.72380118</t>
+          <t>-2508361.086037683</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-839961.0767119527</t>
+          <t>-3261659.578338452</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>39316826.0</t>
+          <t>39500260.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-21.30</t>
+          <t>-22.61</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>54.6</t>
-        </is>
-      </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8066.275</t>
+          <t>3822.13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,51 +10899,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>40.02</v>
+        <v>40.11</v>
       </c>
       <c r="BA22" t="n">
-        <v>39.77</v>
+        <v>39.81</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>108.24</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>469787958.6</v>
+        <v>362638128.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>345844403.0</t>
+          <t>343674934.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>364415966.86</v>
+        <v>363315796.84</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>123943555</t>
+          <t>18963193</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>11702769.29568647</t>
+          <t>9371252.767519468</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>13933513.93885595</t>
+          <t>-3452088.137399018</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,12 +11063,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
@@ -11128,17 +11128,17 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4167.968</t>
+          <t>8066.275</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,87 +11350,87 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-1.45</v>
+        <v>0.05</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>39.98</v>
+        <v>40.02</v>
       </c>
       <c r="BA23" t="n">
-        <v>39.74</v>
+        <v>39.77</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>129.54</t>
+          <t>108.24</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>467047398.4</v>
+        <v>469787958.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>346645174.9</t>
+          <t>345844403.0</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>361420707.74</v>
+        <v>364415966.86</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>120402223</t>
+          <t>123943555</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>11297179.36056474</t>
+          <t>11702769.29568647</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>19249505.79997534</t>
+          <t>13933513.93885595</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,17 +11550,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10398.551</t>
+          <t>4167.968</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>62.16</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.37</v>
+        <v>-1.45</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>39.95</v>
+        <v>39.98</v>
       </c>
       <c r="BA24" t="n">
-        <v>39.71</v>
+        <v>39.74</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>261.75</t>
+          <t>129.54</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-98.51</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>455929202</v>
+        <v>467047398.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>394210697.6</t>
+          <t>346645174.9</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>365467847.18</v>
+        <v>361420707.74</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>61718504</t>
+          <t>120402223</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>9851301.826126453</t>
+          <t>11297179.36056474</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>43839053.96586108</t>
+          <t>19249505.79997534</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,17 +12037,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17316.689</t>
+          <t>10398.551</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.16</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>5.03</v>
+        <v>0.37</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.18</v>
+        <v>1.14</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>39.87</v>
+        <v>39.95</v>
       </c>
       <c r="BA25" t="n">
-        <v>39.7</v>
+        <v>39.71</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>845.58</t>
+          <t>261.75</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-98.51</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>415088503.4</v>
+        <v>455929202</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>369426821.9</t>
+          <t>394210697.6</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>365490619.66</v>
+        <v>365467847.18</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>45661681</t>
+          <t>61718504</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>3671710.527992884</t>
+          <t>9851301.826126453</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>49293584.23977429</t>
+          <t>43839053.96586108</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,17 +12524,17 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16723.374</t>
+          <t>17316.689</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12811,33 +12811,33 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>4.78</v>
+        <v>5.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.98</v>
+        <v>0.18</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>39.71</v>
+        <v>39.87</v>
       </c>
       <c r="BA26" t="n">
-        <v>39.68</v>
+        <v>39.7</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>845.58</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-100.57</t>
+          <t>-99.48</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>691584961.0</t>
+          <t>724944050.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>324711741.2</v>
+        <v>415088503.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>317425091.0</t>
+          <t>369426821.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>358185679.98</v>
+        <v>365490619.66</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>7286650</t>
+          <t>45661681</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-4623175.601421917</t>
+          <t>3671710.527992884</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>23797318.1225155</t>
+          <t>49293584.23977429</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>691584961.0</t>
+          <t>724944050.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>41.95</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>41.2</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8072.809</t>
+          <t>16723.374</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-17.64</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>62.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>2.51</v>
+        <v>4.78</v>
       </c>
       <c r="AV27" t="n">
-        <v>-1.34</v>
+        <v>-0.98</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>39.07000000000001</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>39.6</v>
+        <v>39.71</v>
       </c>
       <c r="BA27" t="n">
-        <v>39.7</v>
+        <v>39.68</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-221.25</t>
+          <t>216.96</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-100.89</t>
+          <t>-100.57</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>319680608.0</t>
+          <t>691584961.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>221900847.4</v>
+        <v>324711741.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>269430245.7</t>
+          <t>317425091.0</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>352970456.12</v>
+        <v>358185679.98</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-47529398</t>
+          <t>7286650</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-9790538.096683266</t>
+          <t>-4623175.601421917</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-9901635.299372643</t>
+          <t>23797318.1225155</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>319680608.0</t>
+          <t>691584961.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,17 +13498,17 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2949.722</t>
+          <t>8072.809</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-17.64</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,33 +13806,33 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>62.07</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-2.15</v>
+        <v>2.51</v>
       </c>
       <c r="AV28" t="n">
-        <v>-1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -13842,30 +13842,30 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>39.07000000000001</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>39.51</v>
+        <v>39.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>39.72</v>
+        <v>39.7</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-1023.06</t>
+          <t>-221.25</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-100.40</t>
+          <t>-100.89</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>112753367.0</t>
+          <t>319680608.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>226242951.4</v>
+        <v>221900847.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>250919193.8</t>
+          <t>269430245.7</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>352572412.46</v>
+        <v>352970456.12</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-24676242</t>
+          <t>-47529398</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-9770338.605285197</t>
+          <t>-9790538.096683266</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-17842472.53423518</t>
+          <t>-9901635.299372643</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>112753367.0</t>
+          <t>319680608.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,17 +13985,17 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5880.808</t>
+          <t>2949.722</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14127,12 +14127,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14308,51 +14308,51 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>-3.58</v>
+        <v>-2.15</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.18</v>
+        <v>-1.06</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>39.6</v>
+        <v>39.51</v>
       </c>
       <c r="BA29" t="n">
-        <v>39.79</v>
+        <v>39.72</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-418.73</t>
+          <t>-1023.06</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>-0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-99.38</t>
+          <t>-100.40</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>226479531.0</t>
+          <t>112753367.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>332492193.2</v>
+        <v>226242951.4</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>258252087.5</t>
+          <t>250919193.8</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>367586169.62</v>
+        <v>352572412.46</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>74240105</t>
+          <t>-24676242</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-8302677.890930655</t>
+          <t>-9770338.605285197</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-6378518.743530452</t>
+          <t>-17842472.53423518</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>226479531.0</t>
+          <t>112753367.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
@@ -14537,17 +14537,17 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6994.968</t>
+          <t>5880.808</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,149 +14599,149 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>28.75</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>38.55</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2025/04/09</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
           <t>38.85</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>5.24</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>2025/04/09</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
       <c r="AI30" t="inlineStr">
         <is>
           <t>2025/11/21</t>
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14795,51 +14795,51 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>-3.02</v>
+        <v>-3.58</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>39.64</v>
+        <v>39.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>39.86</v>
+        <v>39.79</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-418.73</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-98.74</t>
+          <t>-99.38</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>273060239.0</t>
+          <t>226479531.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>323765140.4</v>
+        <v>332492193.2</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>294870086.2</t>
+          <t>258252087.5</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>374398444.12</v>
+        <v>367586169.62</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>28895054</t>
+          <t>74240105</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-8652525.008639783</t>
+          <t>-8302677.890930655</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-1958583.801683307</t>
+          <t>-6378518.743530452</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>273060239.0</t>
+          <t>226479531.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15061,7 +15061,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4472.26</t>
+          <t>6994.968</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,63 +15267,63 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>-1.09</v>
+        <v>-3.02</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.81</v>
+        <v>1.05</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>39.67</v>
+        <v>39.64</v>
       </c>
       <c r="BA31" t="n">
-        <v>39.89</v>
+        <v>39.86</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>199.33</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="BE31" t="n">
         <v>0.05</v>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-98.73</t>
+          <t>-98.74</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>216882274.0485437</t>
+          <t>216905641.6952909</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>177530492.0</t>
+          <t>273060239.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>310138440.8</v>
+        <v>323765140.4</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>299589159.0</t>
+          <t>294870086.2</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>378030653.4</v>
+        <v>374398444.12</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>10549281</t>
+          <t>28895054</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-9869605.228086414</t>
+          <t>-8652525.008639783</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-565231.7489843965</t>
+          <t>-1958583.801683307</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>177530492.0</t>
+          <t>273060239.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2781.739</t>
+          <t>6577.138</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,74 +963,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-11.25</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-25.98</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>95.06</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>12.19</v>
+        <v>11.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>116.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>103.95</v>
+        <v>106.64</v>
       </c>
       <c r="BA2" t="n">
-        <v>81.20999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>66.87</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>11.88</v>
+        <v>12.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.86</v>
+        <v>11.98</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>351042343.0</t>
+          <t>867220860.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>358146601.6</v>
+        <v>424985291.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>483869044.7</t>
+          <t>478872547.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>223785701.76</v>
+        <v>238967669.82</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-125722443</t>
+          <t>-53887256</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>36642132.94028828</t>
+          <t>33988158.0276943</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-17001531.10548103</t>
+          <t>19391296.00842744</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>351042343.0</t>
+          <t>867220860.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>209.76</t>
+          <t>215.85</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2777.39</t>
+          <t>2781.739</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,22 +1460,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>3.77</v>
+        <v>12.19</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.02</v>
+        <v>8.9</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>111.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>101.16</v>
+        <v>103.95</v>
       </c>
       <c r="BA3" t="n">
-        <v>79.94</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>66.87</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>11.17</v>
+        <v>11.88</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>317436210.0</t>
+          <t>351042343.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>340905800.4</v>
+        <v>358146601.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>551077334.7</t>
+          <t>483869044.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>219291632.16</v>
+        <v>223785701.76</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-210171534</t>
+          <t>-125722443</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>46395526.40315542</t>
+          <t>36642132.94028828</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-13079245.47872597</t>
+          <t>-17001531.10548103</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>317436210.0</t>
+          <t>351042343.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>181.71</t>
+          <t>209.76</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1920.967</t>
+          <t>2777.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,149 +1937,149 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>115.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10.81</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-38.14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-35.32</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>44.85</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/07/09</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>45.23</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/07/09</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/03/26</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2025/11/07</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-5.75</v>
+        <v>3.77</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.5</v>
+        <v>10.02</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>111.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>99.02</v>
+        <v>101.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>78.81999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.02</v>
+        <v>11.85</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>199148037.0</t>
+          <t>317436210.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>375506393.4</v>
+        <v>340905800.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>580585132.5</t>
+          <t>551077334.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>215093497.88</v>
+        <v>219291632.16</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-205078739</t>
+          <t>-210171534</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>57209121.29077021</t>
+          <t>46395526.40315542</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-3408207.280549884</t>
+          <t>-13079245.47872597</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>199148037.0</t>
+          <t>317436210.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>156.10</t>
+          <t>181.71</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3681.336</t>
+          <t>1920.967</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.85</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-8.130000000000001</v>
+        <v>-5.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>16.23</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>97.39</v>
+        <v>99.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>77.8</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>12.3</v>
+        <v>11.27</v>
       </c>
       <c r="BE5" t="n">
-        <v>12.21</v>
+        <v>12.02</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>390079006.0</t>
+          <t>199148037.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>457066679.2</v>
+        <v>375506393.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>624826119.2</t>
+          <t>580585132.5</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>211265158</v>
+        <v>215093497.88</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-167759440</t>
+          <t>-205078739</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>68230453.75828296</t>
+          <t>57209121.29077021</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>23203016.08400708</t>
+          <t>-3408207.280549884</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>390079006.0</t>
+          <t>199148037.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>153.66</t>
+          <t>156.10</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4731.625</t>
+          <t>3681.336</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-26.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.87</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>20.95</v>
+        <v>16.23</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>95.5</v>
+        <v>97.39</v>
       </c>
       <c r="BA6" t="n">
-        <v>76.70999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>64.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>13.54</v>
+        <v>12.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>532759803.4</v>
+        <v>457066679.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>644573649.4</t>
+          <t>624826119.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>203514658.18</v>
+        <v>211265158</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-111813846</t>
+          <t>-167759440</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>76417260.6081513</t>
+          <t>68230453.75828296</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>39933480.78037387</t>
+          <t>23203016.08400708</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>179.27</t>
+          <t>153.66</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2274.683</t>
+          <t>4731.625</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>58.37</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>48.73</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>-0.87</v>
       </c>
       <c r="AV7" t="n">
-        <v>24.93</v>
+        <v>20.95</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>115.9</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>92.78</v>
+        <v>95.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>75.31</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>13.86</v>
+        <v>13.54</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.85</v>
+        <v>12.19</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>609591487.8</v>
+        <v>532759803.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>631262663.6</t>
+          <t>644573649.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>192933562.72</v>
+        <v>203514658.18</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-21671175</t>
+          <t>-111813846</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>83050675.12229265</t>
+          <t>76417260.6081513</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>47092048.24731314</t>
+          <t>39933480.78037387</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>186.59</t>
+          <t>179.27</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4247.311</t>
+          <t>2274.683</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>62.52</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>97.28</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>94.43</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="AV8" t="n">
-        <v>26.38</v>
+        <v>24.93</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>89.89</v>
+        <v>92.78</v>
       </c>
       <c r="BA8" t="n">
-        <v>73.78</v>
+        <v>75.31</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>13.75</v>
+        <v>13.86</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.35</v>
+        <v>11.85</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>761248869</v>
+        <v>609591487.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>670874203.7</t>
+          <t>631262663.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>187661356.84</v>
+        <v>192933562.72</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>90374665</t>
+          <t>-21671175</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>89588607.28137983</t>
+          <t>83050675.12229265</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>84371258.084108</t>
+          <t>47092048.24731314</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>182.93</t>
+          <t>186.59</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5223.799</t>
+          <t>4247.311</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.44</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>97.28</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>95.34</t>
+          <t>94.43</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AV9" t="n">
-        <v>28.4</v>
+        <v>26.38</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>113.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>87.15000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="BA9" t="n">
-        <v>72.28</v>
+        <v>73.78</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>61.33</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>13.58</v>
+        <v>13.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.75</v>
+        <v>11.35</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>785663871.6</v>
+        <v>761248869</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>673850359.4</t>
+          <t>670874203.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>177872413.16</v>
+        <v>187661356.84</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>111813512</t>
+          <t>90374665</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>90537216.22633836</t>
+          <t>89588607.28137983</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>110442494.5622396</t>
+          <t>84371258.084108</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>178.05</t>
+          <t>182.93</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4802,17 +4802,17 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6754.556</t>
+          <t>5223.799</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>11.97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>53.80</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.34</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>6.24</v>
+        <v>1.88</v>
       </c>
       <c r="AV10" t="n">
-        <v>29.07</v>
+        <v>28.4</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>108.72</t>
+          <t>111.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>84.23999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>70.81999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.04</v>
+        <v>10.75</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>25176856.23407202</t>
+          <t>26941246.87551867</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>768544627.0</t>
+          <t>606949466.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>792585559.2</v>
+        <v>785663871.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>627953016.8</t>
+          <t>673850359.4</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>165738491.38</v>
+        <v>177872413.16</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>164632542</t>
+          <t>111813512</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>86918074.71071994</t>
+          <t>90537216.22633836</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>131259497.8323476</t>
+          <t>110442494.5622396</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>768544627.0</t>
+          <t>606949466.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>181.71</t>
+          <t>178.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>145.51</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2401.338</t>
+          <t>1001.906</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,38 +5527,38 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -5567,26 +5567,26 @@
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>53.52</v>
+        <v>53.54</v>
       </c>
       <c r="BA11" t="n">
-        <v>55.03</v>
+        <v>54.89</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>59.61</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.89</t>
+          <t>-109.62</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>128355810.0</t>
+          <t>53038707.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>64220047</v>
+        <v>66160708</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>54551291.2</t>
+          <t>55912240.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>69959828.64</v>
+        <v>69453118.3</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>9668755</t>
+          <t>10248467</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3134466.890105174</t>
+          <t>-2347067.091340641</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>3289043.947319031</t>
+          <t>1983631.801864296</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>128355810.0</t>
+          <t>53038707.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,14 +5716,14 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
       <c r="CH11" t="inlineStr">
         <is>
           <t>4.52</t>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1128.585</t>
+          <t>2401.338</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-30.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.6</v>
+        <v>-1.53</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>52.68000000000001</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>53.54</v>
+        <v>53.52</v>
       </c>
       <c r="BA12" t="n">
-        <v>55.21</v>
+        <v>55.03</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>59.91</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-109.89</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>59435920.0</t>
+          <t>128355810.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>46846616</v>
+        <v>64220047</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>45326784.0</t>
+          <t>54551291.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>68837502.5</v>
+        <v>69959828.64</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>1519832</t>
+          <t>9668755</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-4302377.95145503</t>
+          <t>-3134466.890105174</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3033237.021578461</t>
+          <t>3289043.947319031</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>59435920.0</t>
+          <t>128355810.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>711.499</t>
+          <t>1128.585</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-31.44</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.7</v>
+        <v>0.61</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1.36</v>
+        <v>-1.6</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.68000000000001</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>53.53</v>
+        <v>53.54</v>
       </c>
       <c r="BA13" t="n">
-        <v>55.37</v>
+        <v>55.21</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>59.91</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>37249048.0</t>
+          <t>59435920.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>44167713</v>
+        <v>46846616</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>45002856.4</t>
+          <t>45326784.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>69116768.45999999</v>
+        <v>68837502.5</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-835143</t>
+          <t>1519832</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-4533130.847796224</t>
+          <t>-4302377.95145503</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-4572463.15494708</t>
+          <t>-3033237.021578461</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>37249048.0</t>
+          <t>59435920.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-24.78</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1007.736</t>
+          <t>711.499</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-31.44</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7007,44 +7007,44 @@
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.27</v>
+        <v>-1.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.34</v>
+        <v>-1.36</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>53.56</v>
+        <v>53.53</v>
       </c>
       <c r="BA14" t="n">
-        <v>55.53</v>
+        <v>55.37</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.61</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BE14" t="n">
         <v>-0.72</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-110.33</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>52724055.0</t>
+          <t>37249048.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>43773654.8</v>
+        <v>44167713</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>45227977.6</t>
+          <t>45002856.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>69838946.16</v>
+        <v>69116768.45999999</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-1454322</t>
+          <t>-835143</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4525979.519223342</t>
+          <t>-4533130.847796224</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-4230890.51851128</t>
+          <t>-4572463.15494708</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>52724055.0</t>
+          <t>37249048.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-24.78</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7279,42 +7279,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1007.736</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>809.469</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.48</v>
+        <v>-1.27</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.59</v>
+        <v>-0.34</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>53.58</v>
+        <v>53.56</v>
       </c>
       <c r="BA15" t="n">
-        <v>55.68</v>
+        <v>55.53</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.57</v>
+        <v>-0.61</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-110.75</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>45663772.6</v>
+        <v>43773654.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>43887254.7</t>
+          <t>45227977.6</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>70595577.38</v>
+        <v>69838946.16</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>1776517</t>
+          <t>-1454322</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-4579632.064807353</t>
+          <t>-4525979.519223342</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-5249862.840799026</t>
+          <t>-4230890.51851128</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>784.817</t>
+          <t>809.469</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-2.41</v>
+        <v>-1.48</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>53.66</v>
+        <v>53.58</v>
       </c>
       <c r="BA16" t="n">
-        <v>55.83</v>
+        <v>55.68</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-111.39</t>
+          <t>-110.75</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>44882535.4</v>
+        <v>45663772.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>44153034.1</t>
+          <t>43887254.7</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>71382431.34</v>
+        <v>70595577.38</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>1776517</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-4457771.923717958</t>
+          <t>-4579632.064807353</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-5512115.378324404</t>
+          <t>-5249862.840799026</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
           <t>54.2</t>
         </is>
       </c>
-      <c r="CR16" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>847.176</t>
+          <t>784.817</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.78</v>
+        <v>-2.41</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>53.68</v>
+        <v>53.66</v>
       </c>
       <c r="BA17" t="n">
-        <v>56</v>
+        <v>55.83</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-112.22</t>
+          <t>-111.39</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>43806952</v>
+        <v>44882535.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>47872049.3</t>
+          <t>44153034.1</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>71746544.26000001</v>
+        <v>71382431.34</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-4065097</t>
+          <t>729501</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-4266073.113789514</t>
+          <t>-4457771.923717958</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-5492034.846991934</t>
+          <t>-5512115.378324404</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>643.823</t>
+          <t>847.176</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-32.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.29</v>
+        <v>-0.78</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.67</v>
+        <v>53.68</v>
       </c>
       <c r="BA18" t="n">
-        <v>56.14</v>
+        <v>56</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>61.68</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.86</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-112.22</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>45837999.8</v>
+        <v>43806952</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>67426005.1</t>
+          <t>47872049.3</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>73613007.12</v>
+        <v>71746544.26000001</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-21588005</t>
+          <t>-4065097</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-4043170.980479982</t>
+          <t>-4266073.113789514</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-5754998.914838694</t>
+          <t>-5492034.846991934</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1133.708</t>
+          <t>643.823</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.38</t>
+          <t>-32.02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>53.81999999999999</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.5</v>
+        <v>53.67</v>
       </c>
       <c r="BA19" t="n">
-        <v>56.28</v>
+        <v>56.14</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>61.94</t>
+          <t>61.68</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.63</v>
+        <v>-0.51</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-115.04</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>489574079.0813794</t>
+          <t>489009318.7252066</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>62174644.0</t>
+          <t>35278757.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>46682300.4</v>
+        <v>45837999.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>69037086.7</t>
+          <t>67426005.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>76055049.48</v>
+        <v>73613007.12</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-22354786</t>
+          <t>-21588005</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-3731929.537869307</t>
+          <t>-4043170.980479982</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-4771985.336232685</t>
+          <t>-5754998.914838694</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>62174644.0</t>
+          <t>35278757.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-19.86</t>
+          <t>-20.58</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
           <t>54.4</t>
         </is>
       </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>33489.271</t>
+          <t>83779.541</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,74 +9729,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>48.74</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>46.1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>46.1</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>42.5</t>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9925,51 +9925,51 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>9.27</v>
+        <v>14.89</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.9</v>
+        <v>7.25</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>40.6</v>
+        <v>41.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>40.07</v>
+        <v>40.33</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>132.01</t>
+          <t>157.56</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-86.03</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>1518087925.0</t>
+          <t>4137211057.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>602305833</v>
+        <v>1363071362.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>534676615.7</t>
+          <t>916429660.6</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>403088648.8</v>
+        <v>481812681.56</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>67629217</t>
+          <t>446641701</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>24361231.7261386</t>
+          <t>75754763.69988593</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>108529886.1159553</t>
+          <t>358419189.5554962</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>1518087925.0</t>
+          <t>4137211057.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20045.708</t>
+          <t>33489.271</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,22 +10226,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-15.68</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10412,51 +10412,51 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>81.98</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>2.29</v>
+        <v>9.27</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.84</v>
+        <v>3.9</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>41.01000000000001</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>40.27</v>
+        <v>40.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>39.92</v>
+        <v>40.07</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>132.01</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-94.33</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>846499164.0</t>
+          <t>1518087925.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>332357117.8</v>
+        <v>602305833</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>394143159.9</t>
+          <t>534676615.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>375094315.86</v>
+        <v>403088648.8</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-61786042</t>
+          <t>67629217</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>9057840.018899202</t>
+          <t>24361231.7261386</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>28289435.1267556</t>
+          <t>108529886.1159553</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>846499164.0</t>
+          <t>1518087925.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3860.221</t>
+          <t>20045.708</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-24.97</t>
+          <t>-15.68</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>81.98</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.42</v>
+        <v>2.29</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>41.01000000000001</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>40.16</v>
+        <v>40.27</v>
       </c>
       <c r="BA22" t="n">
-        <v>39.85</v>
+        <v>39.92</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-95.39</t>
+          <t>-94.33</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>157722857.0</t>
+          <t>846499164.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>249193889.8</v>
+        <v>332357117.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>332141196.6</t>
+          <t>394143159.9</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>362488533.18</v>
+        <v>375094315.86</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-82947306</t>
+          <t>-61786042</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>5561186.362925313</t>
+          <t>9057840.018899202</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-15394178.86234254</t>
+          <t>28289435.1267556</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>157722857.0</t>
+          <t>846499164.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,42 +11175,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3860.221</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>3822.13</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>-24.97</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>73.42</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>40.11</v>
+        <v>40.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>39.81</v>
+        <v>39.85</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-95.39</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>155835810.0</t>
+          <t>157722857.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>362638128.4</v>
+        <v>249193889.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>343674934.8</t>
+          <t>332141196.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>363315796.84</v>
+        <v>362488533.18</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>18963193</t>
+          <t>-82947306</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>9371252.767519468</t>
+          <t>5561186.362925313</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-3452088.137399018</t>
+          <t>-15394178.86234254</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>155835810.0</t>
+          <t>157722857.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8066.275</t>
+          <t>3822.13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11873,51 +11873,51 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>40.02</v>
+        <v>40.11</v>
       </c>
       <c r="BA24" t="n">
-        <v>39.77</v>
+        <v>39.81</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>108.24</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>469787958.6</v>
+        <v>362638128.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>345844403.0</t>
+          <t>343674934.8</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>364415966.86</v>
+        <v>363315796.84</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>123943555</t>
+          <t>18963193</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>11702769.29568647</t>
+          <t>9371252.767519468</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>13933513.93885595</t>
+          <t>-3452088.137399018</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,17 +12102,17 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4167.968</t>
+          <t>8066.275</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,92 +12319,92 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-1.45</v>
+        <v>0.05</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>39.98</v>
+        <v>40.02</v>
       </c>
       <c r="BA25" t="n">
-        <v>39.74</v>
+        <v>39.77</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>129.54</t>
+          <t>108.24</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>467047398.4</v>
+        <v>469787958.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>346645174.9</t>
+          <t>345844403.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>361420707.74</v>
+        <v>364415966.86</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>120402223</t>
+          <t>123943555</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>11297179.36056474</t>
+          <t>11702769.29568647</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>19249505.79997534</t>
+          <t>13933513.93885595</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10398.551</t>
+          <t>4167.968</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,22 +12806,22 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>62.16</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0.37</v>
+        <v>-1.45</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>39.95</v>
+        <v>39.98</v>
       </c>
       <c r="BA26" t="n">
-        <v>39.71</v>
+        <v>39.74</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>261.75</t>
+          <t>129.54</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-98.51</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>455929202</v>
+        <v>467047398.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>394210697.6</t>
+          <t>346645174.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>365467847.18</v>
+        <v>361420707.74</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>61718504</t>
+          <t>120402223</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>9851301.826126453</t>
+          <t>11297179.36056474</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>43839053.96586108</t>
+          <t>19249505.79997534</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17316.689</t>
+          <t>10398.551</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.16</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>5.03</v>
+        <v>0.37</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.18</v>
+        <v>1.14</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>39.87</v>
+        <v>39.95</v>
       </c>
       <c r="BA27" t="n">
-        <v>39.7</v>
+        <v>39.71</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>845.58</t>
+          <t>261.75</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-98.51</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>415088503.4</v>
+        <v>455929202</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>369426821.9</t>
+          <t>394210697.6</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>365490619.66</v>
+        <v>365467847.18</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>45661681</t>
+          <t>61718504</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>3671710.527992884</t>
+          <t>9851301.826126453</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>49293584.23977429</t>
+          <t>43839053.96586108</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16723.374</t>
+          <t>17316.689</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13780,38 +13780,38 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>4.78</v>
+        <v>5.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.98</v>
+        <v>0.18</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>39.71</v>
+        <v>39.87</v>
       </c>
       <c r="BA28" t="n">
-        <v>39.68</v>
+        <v>39.7</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>845.58</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-100.57</t>
+          <t>-99.48</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>221226673.4110345</t>
+          <t>229469910.2045454</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>691584961.0</t>
+          <t>724944050.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>324711741.2</v>
+        <v>415088503.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>317425091.0</t>
+          <t>369426821.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>358185679.98</v>
+        <v>365490619.66</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>7286650</t>
+          <t>45661681</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-4623175.601421917</t>
+          <t>3671710.527992884</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>23797318.1225155</t>
+          <t>49293584.23977429</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>691584961.0</t>
+          <t>724944050.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>41.95</t>
-        </is>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>41.2</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6577.138</t>
+          <t>7785.805</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>80.19</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>95.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>11.45</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.960000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>116.2</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>106.64</v>
+        <v>109.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>82.41</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>69.13</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.98</v>
+        <v>12.19</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>867220860.0</t>
+          <t>1061252730.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>424985291.2</v>
+        <v>559220036</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>478872547.3</t>
+          <t>508143357.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>238967669.82</v>
+        <v>259133357.92</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-53887256</t>
+          <t>51076678</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>33988158.0276943</t>
+          <t>37825961.84465712</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>19391296.00842744</t>
+          <t>58933882.83795261</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>867220860.0</t>
+          <t>1061252730.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>215.85</t>
+          <t>220.73</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2781.739</t>
+          <t>6577.138</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,177 +1450,177 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-11.25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-25.98</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>44.85</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/07/09</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2025-12-02 00:00:00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/07/09</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/03/26</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,51 +1646,51 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>95.06</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>12.19</v>
+        <v>11.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>116.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>103.95</v>
+        <v>106.64</v>
       </c>
       <c r="BA3" t="n">
-        <v>81.20999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>66.87</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>11.88</v>
+        <v>12.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.86</v>
+        <v>11.98</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>351042343.0</t>
+          <t>867220860.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>358146601.6</v>
+        <v>424985291.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>483869044.7</t>
+          <t>478872547.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>223785701.76</v>
+        <v>238967669.82</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-125722443</t>
+          <t>-53887256</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>36642132.94028828</t>
+          <t>33988158.0276943</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-17001531.10548103</t>
+          <t>19391296.00842744</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>351042343.0</t>
+          <t>867220860.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>209.76</t>
+          <t>215.85</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2777.39</t>
+          <t>2781.739</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,22 +1947,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>3.77</v>
+        <v>12.19</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.02</v>
+        <v>8.9</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>111.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>101.16</v>
+        <v>103.95</v>
       </c>
       <c r="BA4" t="n">
-        <v>79.94</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>66.87</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>11.17</v>
+        <v>11.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>317436210.0</t>
+          <t>351042343.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>340905800.4</v>
+        <v>358146601.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>551077334.7</t>
+          <t>483869044.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>219291632.16</v>
+        <v>223785701.76</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-210171534</t>
+          <t>-125722443</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>46395526.40315542</t>
+          <t>36642132.94028828</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-13079245.47872597</t>
+          <t>-17001531.10548103</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>317436210.0</t>
+          <t>351042343.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>181.71</t>
+          <t>209.76</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1920.967</t>
+          <t>2777.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,177 +2424,177 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>115.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12.17</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-38.14</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-35.32</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>44.85</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/07/09</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>2025-12-02 00:00:00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>45.23</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/07/09</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/03/26</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-5.75</v>
+        <v>3.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>12.5</v>
+        <v>10.02</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>111.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>99.02</v>
+        <v>101.16</v>
       </c>
       <c r="BA5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>12.02</v>
+        <v>11.85</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>199148037.0</t>
+          <t>317436210.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>375506393.4</v>
+        <v>340905800.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>580585132.5</t>
+          <t>551077334.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>215093497.88</v>
+        <v>219291632.16</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-205078739</t>
+          <t>-210171534</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>57209121.29077021</t>
+          <t>46395526.40315542</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-3408207.280549884</t>
+          <t>-13079245.47872597</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>199148037.0</t>
+          <t>317436210.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>156.10</t>
+          <t>181.71</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3681.336</t>
+          <t>1920.967</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.85</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-8.130000000000001</v>
+        <v>-5.75</v>
       </c>
       <c r="AV6" t="n">
-        <v>16.23</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>97.39</v>
+        <v>99.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>77.8</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>12.3</v>
+        <v>11.27</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.21</v>
+        <v>12.02</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>390079006.0</t>
+          <t>199148037.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>457066679.2</v>
+        <v>375506393.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>624826119.2</t>
+          <t>580585132.5</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>211265158</v>
+        <v>215093497.88</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-167759440</t>
+          <t>-205078739</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>68230453.75828296</t>
+          <t>57209121.29077021</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>23203016.08400708</t>
+          <t>-3408207.280549884</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>390079006.0</t>
+          <t>199148037.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>153.66</t>
+          <t>156.10</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4731.625</t>
+          <t>3681.336</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-26.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.87</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>20.95</v>
+        <v>16.23</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>95.5</v>
+        <v>97.39</v>
       </c>
       <c r="BA7" t="n">
-        <v>76.70999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>64.04</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>13.54</v>
+        <v>12.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>532759803.4</v>
+        <v>457066679.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>644573649.4</t>
+          <t>624826119.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>203514658.18</v>
+        <v>211265158</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-111813846</t>
+          <t>-167759440</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>76417260.6081513</t>
+          <t>68230453.75828296</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>39933480.78037387</t>
+          <t>23203016.08400708</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>179.27</t>
+          <t>153.66</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2274.683</t>
+          <t>4731.625</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>58.37</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>48.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.38</v>
+        <v>-0.87</v>
       </c>
       <c r="AV8" t="n">
-        <v>24.93</v>
+        <v>20.95</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>115.9</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>92.78</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>75.31</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>13.86</v>
+        <v>13.54</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.85</v>
+        <v>12.19</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>609591487.8</v>
+        <v>532759803.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>631262663.6</t>
+          <t>644573649.4</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>192933562.72</v>
+        <v>203514658.18</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-21671175</t>
+          <t>-111813846</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>83050675.12229265</t>
+          <t>76417260.6081513</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>47092048.24731314</t>
+          <t>39933480.78037387</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>186.59</t>
+          <t>179.27</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4247.311</t>
+          <t>2274.683</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>62.52</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>97.28</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>94.43</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="AV9" t="n">
-        <v>26.38</v>
+        <v>24.93</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>89.89</v>
+        <v>92.78</v>
       </c>
       <c r="BA9" t="n">
-        <v>73.78</v>
+        <v>75.31</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>13.75</v>
+        <v>13.86</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.35</v>
+        <v>11.85</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>761248869</v>
+        <v>609591487.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>670874203.7</t>
+          <t>631262663.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>187661356.84</v>
+        <v>192933562.72</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>90374665</t>
+          <t>-21671175</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>89588607.28137983</t>
+          <t>83050675.12229265</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>84371258.084108</t>
+          <t>47092048.24731314</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>182.93</t>
+          <t>186.59</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5223.799</t>
+          <t>4247.311</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.44</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>97.28</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>95.34</t>
+          <t>94.43</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AV10" t="n">
-        <v>28.4</v>
+        <v>26.38</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>113.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>87.15000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="BA10" t="n">
-        <v>72.28</v>
+        <v>73.78</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>61.33</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>13.58</v>
+        <v>13.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.75</v>
+        <v>11.35</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26941246.87551867</t>
+          <t>42517061.96926229</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>785663871.6</v>
+        <v>761248869</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>673850359.4</t>
+          <t>670874203.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>177872413.16</v>
+        <v>187661356.84</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>111813512</t>
+          <t>90374665</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>90537216.22633836</t>
+          <t>89588607.28137983</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>110442494.5622396</t>
+          <t>84371258.084108</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>606949466.0</t>
+          <t>490439175.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>178.05</t>
+          <t>182.93</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>145.51</t>
+          <t>147.75</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1001.906</t>
+          <t>1205.381</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5501,22 +5501,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.76</v>
+        <v>0.61</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.58</v>
+        <v>-1.28</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.78000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>53.54</v>
+        <v>53.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>54.89</v>
+        <v>54.74</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.16</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.6</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.67</v>
+        <v>-0.65</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.62</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>53038707.0</t>
+          <t>63546872.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>66160708</v>
+        <v>68325271.40000001</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>55912240.3</t>
+          <t>56049463.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>69453118.3</v>
+        <v>68877612.31999999</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>10248467</t>
+          <t>12275808</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2347067.091340641</t>
+          <t>-1707769.864980638</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1983631.801864296</t>
+          <t>1808364.879999377</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>53038707.0</t>
+          <t>63546872.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2401.338</t>
+          <t>1001.906</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5988,22 +5988,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,38 +6014,38 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -6054,26 +6054,26 @@
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>53.52</v>
+        <v>53.54</v>
       </c>
       <c r="BA12" t="n">
-        <v>55.03</v>
+        <v>54.89</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>59.61</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-109.89</t>
+          <t>-109.62</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>128355810.0</t>
+          <t>53038707.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>64220047</v>
+        <v>66160708</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>54551291.2</t>
+          <t>55912240.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>69959828.64</v>
+        <v>69453118.3</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>9668755</t>
+          <t>10248467</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3134466.890105174</t>
+          <t>-2347067.091340641</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>3289043.947319031</t>
+          <t>1983631.801864296</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>128355810.0</t>
+          <t>53038707.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,14 +6203,14 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
       <c r="CH12" t="inlineStr">
         <is>
           <t>4.52</t>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1128.585</t>
+          <t>2401.338</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-30.25</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6475,22 +6475,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1.6</v>
+        <v>-1.53</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>52.68000000000001</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>53.54</v>
+        <v>53.52</v>
       </c>
       <c r="BA13" t="n">
-        <v>55.21</v>
+        <v>55.03</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>59.91</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-109.89</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>59435920.0</t>
+          <t>128355810.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>46846616</v>
+        <v>64220047</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>45326784.0</t>
+          <t>54551291.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>68837502.5</v>
+        <v>69959828.64</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>1519832</t>
+          <t>9668755</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-4302377.95145503</t>
+          <t>-3134466.890105174</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-3033237.021578461</t>
+          <t>3289043.947319031</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>59435920.0</t>
+          <t>128355810.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>711.499</t>
+          <t>1128.585</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-31.44</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6962,22 +6962,22 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.7</v>
+        <v>0.61</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.36</v>
+        <v>-1.6</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.68000000000001</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>53.53</v>
+        <v>53.54</v>
       </c>
       <c r="BA14" t="n">
-        <v>55.37</v>
+        <v>55.21</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>59.91</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>37249048.0</t>
+          <t>59435920.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>44167713</v>
+        <v>46846616</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>45002856.4</t>
+          <t>45326784.0</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>69116768.45999999</v>
+        <v>68837502.5</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-835143</t>
+          <t>1519832</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4533130.847796224</t>
+          <t>-4302377.95145503</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-4572463.15494708</t>
+          <t>-3033237.021578461</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>37249048.0</t>
+          <t>59435920.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-24.78</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1007.736</t>
+          <t>711.499</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-31.44</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7449,22 +7449,22 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,12 +7475,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7494,44 +7494,44 @@
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.27</v>
+        <v>-1.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.34</v>
+        <v>-1.36</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>53.56</v>
+        <v>53.53</v>
       </c>
       <c r="BA15" t="n">
-        <v>55.53</v>
+        <v>55.37</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.61</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BE15" t="n">
         <v>-0.72</v>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-110.33</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>52724055.0</t>
+          <t>37249048.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>43773654.8</v>
+        <v>44167713</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>45227977.6</t>
+          <t>45002856.4</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>69838946.16</v>
+        <v>69116768.45999999</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-1454322</t>
+          <t>-835143</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-4525979.519223342</t>
+          <t>-4533130.847796224</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-4230890.51851128</t>
+          <t>-4572463.15494708</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>52724055.0</t>
+          <t>37249048.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-24.78</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,42 +7766,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1007.736</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>809.469</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7936,22 +7936,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.48</v>
+        <v>-1.27</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.59</v>
+        <v>-0.34</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>53.58</v>
+        <v>53.56</v>
       </c>
       <c r="BA16" t="n">
-        <v>55.68</v>
+        <v>55.53</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.57</v>
+        <v>-0.61</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-110.75</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>45663772.6</v>
+        <v>43773654.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>43887254.7</t>
+          <t>45227977.6</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>70595577.38</v>
+        <v>69838946.16</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>1776517</t>
+          <t>-1454322</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-4579632.064807353</t>
+          <t>-4525979.519223342</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-5249862.840799026</t>
+          <t>-4230890.51851128</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>784.817</t>
+          <t>809.469</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-2.41</v>
+        <v>-1.48</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>53.66</v>
+        <v>53.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>55.83</v>
+        <v>55.68</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-111.39</t>
+          <t>-110.75</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>44882535.4</v>
+        <v>45663772.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>44153034.1</t>
+          <t>43887254.7</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>71382431.34</v>
+        <v>70595577.38</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>1776517</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-4457771.923717958</t>
+          <t>-4579632.064807353</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-5512115.378324404</t>
+          <t>-5249862.840799026</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
           <t>54.2</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>847.176</t>
+          <t>784.817</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8910,22 +8910,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.78</v>
+        <v>-2.41</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.68</v>
+        <v>53.66</v>
       </c>
       <c r="BA18" t="n">
-        <v>56</v>
+        <v>55.83</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-112.22</t>
+          <t>-111.39</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>43806952</v>
+        <v>44882535.4</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>47872049.3</t>
+          <t>44153034.1</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>71746544.26000001</v>
+        <v>71382431.34</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-4065097</t>
+          <t>729501</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-4266073.113789514</t>
+          <t>-4457771.923717958</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-5492034.846991934</t>
+          <t>-5512115.378324404</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>643.823</t>
+          <t>847.176</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9397,22 +9397,22 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.29</v>
+        <v>-0.78</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.67</v>
+        <v>53.68</v>
       </c>
       <c r="BA19" t="n">
-        <v>56.14</v>
+        <v>56</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>61.68</t>
+          <t>61.42</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.86</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-112.22</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>489009318.7252066</t>
+          <t>701654341.9487705</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>45837999.8</v>
+        <v>43806952</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>67426005.1</t>
+          <t>47872049.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>73613007.12</v>
+        <v>71746544.26000001</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-21588005</t>
+          <t>-4065097</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-4043170.980479982</t>
+          <t>-4266073.113789514</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-5754998.914838694</t>
+          <t>-5492034.846991934</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>35278757.0</t>
+          <t>46041405.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>83779.541</t>
+          <t>127396.434</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>48.74</t>
+          <t>76.29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9929,47 +9929,47 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>14.89</v>
+        <v>18.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.25</v>
+        <v>12.26</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>47.07</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>41.14</v>
+        <v>41.93</v>
       </c>
       <c r="BA20" t="n">
-        <v>40.33</v>
+        <v>40.65</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>157.56</t>
+          <t>154.82</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1.48</v>
+        <v>2.39</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-86.03</t>
+          <t>-77.21</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>4137211057.0</t>
+          <t>6820687164.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>1363071362.6</v>
+        <v>2696041633.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>916429660.6</t>
+          <t>1529339880.9</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>481812681.56</v>
+        <v>607014963.9</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>446641701</t>
+          <t>1166701752</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>75754763.69988593</t>
+          <t>175737404.7074862</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>358419189.5554962</t>
+          <t>725641930.2492876</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>4137211057.0</t>
+          <t>6820687164.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>50.7</t>
         </is>
       </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>46.55</t>
-        </is>
-      </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33489.271</t>
+          <t>83779.541</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,74 +10216,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8.98</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>48.74</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>46.1</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>9.07</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>46.1</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>42.5</t>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>65.76</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10412,51 +10412,51 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>9.27</v>
+        <v>14.89</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.9</v>
+        <v>7.25</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>40.6</v>
+        <v>41.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>40.07</v>
+        <v>40.33</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>132.01</t>
+          <t>157.56</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-86.03</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>1518087925.0</t>
+          <t>4137211057.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>602305833</v>
+        <v>1363071362.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>534676615.7</t>
+          <t>916429660.6</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>403088648.8</v>
+        <v>481812681.56</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>67629217</t>
+          <t>446641701</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>24361231.7261386</t>
+          <t>75754763.69988593</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>108529886.1159553</t>
+          <t>358419189.5554962</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>1518087925.0</t>
+          <t>4137211057.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20045.708</t>
+          <t>33489.271</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,22 +10713,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-15.68</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>26.29</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,51 +10899,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>81.98</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>2.29</v>
+        <v>9.27</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.84</v>
+        <v>3.9</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41.01000000000001</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>40.27</v>
+        <v>40.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>39.92</v>
+        <v>40.07</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>132.01</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-94.33</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>846499164.0</t>
+          <t>1518087925.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>332357117.8</v>
+        <v>602305833</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>394143159.9</t>
+          <t>534676615.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>375094315.86</v>
+        <v>403088648.8</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-61786042</t>
+          <t>67629217</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>9057840.018899202</t>
+          <t>24361231.7261386</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>28289435.1267556</t>
+          <t>108529886.1159553</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>846499164.0</t>
+          <t>1518087925.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3860.221</t>
+          <t>20045.708</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-24.97</t>
+          <t>-15.68</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>81.98</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.42</v>
+        <v>2.29</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>41.01000000000001</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>40.16</v>
+        <v>40.27</v>
       </c>
       <c r="BA23" t="n">
-        <v>39.85</v>
+        <v>39.92</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-95.39</t>
+          <t>-94.33</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>157722857.0</t>
+          <t>846499164.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>249193889.8</v>
+        <v>332357117.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>332141196.6</t>
+          <t>394143159.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>362488533.18</v>
+        <v>375094315.86</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-82947306</t>
+          <t>-61786042</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>5561186.362925313</t>
+          <t>9057840.018899202</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-15394178.86234254</t>
+          <t>28289435.1267556</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>157722857.0</t>
+          <t>846499164.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3822.13</t>
+          <t>3860.221</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>-24.97</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>73.42</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>40.11</v>
+        <v>40.16</v>
       </c>
       <c r="BA24" t="n">
-        <v>39.81</v>
+        <v>39.85</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-95.39</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>155835810.0</t>
+          <t>157722857.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>362638128.4</v>
+        <v>249193889.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>343674934.8</t>
+          <t>332141196.6</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>363315796.84</v>
+        <v>362488533.18</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>18963193</t>
+          <t>-82947306</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>9371252.767519468</t>
+          <t>5561186.362925313</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-3452088.137399018</t>
+          <t>-15394178.86234254</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>155835810.0</t>
+          <t>157722857.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8066.275</t>
+          <t>3822.13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12174,109 +12174,109 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
           <t>2025/10/21</t>
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>40.02</v>
+        <v>40.11</v>
       </c>
       <c r="BA25" t="n">
-        <v>39.77</v>
+        <v>39.81</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>108.24</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>469787958.6</v>
+        <v>362638128.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>345844403.0</t>
+          <t>343674934.8</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>364415966.86</v>
+        <v>363315796.84</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>123943555</t>
+          <t>18963193</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>11702769.29568647</t>
+          <t>9371252.767519468</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>13933513.93885595</t>
+          <t>-3452088.137399018</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,17 +12589,17 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4167.968</t>
+          <t>8066.275</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,92 +12806,92 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-1.45</v>
+        <v>0.05</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>39.98</v>
+        <v>40.02</v>
       </c>
       <c r="BA26" t="n">
-        <v>39.74</v>
+        <v>39.77</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>129.54</t>
+          <t>108.24</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>467047398.4</v>
+        <v>469787958.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>346645174.9</t>
+          <t>345844403.0</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>361420707.74</v>
+        <v>364415966.86</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>120402223</t>
+          <t>123943555</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>11297179.36056474</t>
+          <t>11702769.29568647</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>19249505.79997534</t>
+          <t>13933513.93885595</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10398.551</t>
+          <t>4167.968</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>62.16</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.37</v>
+        <v>-1.45</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>39.95</v>
+        <v>39.98</v>
       </c>
       <c r="BA27" t="n">
-        <v>39.71</v>
+        <v>39.74</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>261.75</t>
+          <t>129.54</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-98.51</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>455929202</v>
+        <v>467047398.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>394210697.6</t>
+          <t>346645174.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>365467847.18</v>
+        <v>361420707.74</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>61718504</t>
+          <t>120402223</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>9851301.826126453</t>
+          <t>11297179.36056474</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>43839053.96586108</t>
+          <t>19249505.79997534</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17316.689</t>
+          <t>10398.551</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>127396</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.16</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>5.03</v>
+        <v>0.37</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.18</v>
+        <v>1.14</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>39.87</v>
+        <v>39.94</v>
       </c>
       <c r="BA28" t="n">
-        <v>39.7</v>
+        <v>39.71</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>845.58</t>
+          <t>261.75</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-98.51</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>229469910.2045454</t>
+          <t>327389967.3872951</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>415088503.4</v>
+        <v>455929202</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>369426821.9</t>
+          <t>394210697.6</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>365490619.66</v>
+        <v>365467847.18</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>45661681</t>
+          <t>61718504</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>3671710.527992884</t>
+          <t>9851301.826126453</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>49293584.23977429</t>
+          <t>43839053.96586108</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>724944050.0</t>
+          <t>430683024.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>58.04</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/聚亞醯胺樹脂.xlsx
+++ b/Result/checksun_type/聚亞醯胺樹脂.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7785.805</t>
+          <t>2598.798</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>80.19</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,75 +1144,75 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>67.27</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>8.050000000000001</v>
+        <v>-2.16</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.14</v>
+        <v>12.25</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>121.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>109.5</v>
+        <v>111.54</v>
       </c>
       <c r="BA2" t="n">
-        <v>83.51000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>69.13</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>13</v>
+        <v>12.53</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.19</v>
+        <v>12.26</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1061252730.0</t>
+          <t>328777874.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>559220036</v>
+        <v>585146003.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>508143357.6</t>
+          <t>480326198.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>259133357.92</v>
+        <v>264228625.56</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>51076678</t>
+          <t>104819805</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>37825961.84465712</t>
+          <t>36653464.99896701</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>58933882.83795261</t>
+          <t>30204732.34767139</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1061252730.0</t>
+          <t>328777874.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>220.73</t>
+          <t>198.78</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6577.138</t>
+          <t>7785.805</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>80.19</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,60 +1646,60 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>95.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>11.45</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.960000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>116.2</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>106.64</v>
+        <v>109.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>82.41</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>69.13</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.98</v>
+        <v>12.19</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>867220860.0</t>
+          <t>1061252730.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>424985291.2</v>
+        <v>559220036</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>478872547.3</t>
+          <t>508143357.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>238967669.82</v>
+        <v>259133357.92</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-53887256</t>
+          <t>51076678</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>33988158.0276943</t>
+          <t>37825961.84465712</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>19391296.00842744</t>
+          <t>58933882.83795261</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>867220860.0</t>
+          <t>1061252730.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>215.85</t>
+          <t>220.73</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2781.739</t>
+          <t>6577.138</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,177 +1937,177 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-5.71</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-11.25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-25.98</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>44.85</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/07/09</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>2025-12-02 00:00:00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/07/09</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/03/26</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,60 +2133,60 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>95.06</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>12.19</v>
+        <v>11.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>116.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>103.95</v>
+        <v>106.64</v>
       </c>
       <c r="BA4" t="n">
-        <v>81.20999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>66.87</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>11.88</v>
+        <v>12.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.86</v>
+        <v>11.98</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>351042343.0</t>
+          <t>867220860.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>358146601.6</v>
+        <v>424985291.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>483869044.7</t>
+          <t>478872547.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>223785701.76</v>
+        <v>238967669.82</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-125722443</t>
+          <t>-53887256</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>36642132.94028828</t>
+          <t>33988158.0276943</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-17001531.10548103</t>
+          <t>19391296.00842744</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>351042343.0</t>
+          <t>867220860.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>209.76</t>
+          <t>215.85</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2777.39</t>
+          <t>2781.739</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,75 +2605,75 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>3.77</v>
+        <v>12.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.02</v>
+        <v>8.9</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>111.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>101.16</v>
+        <v>103.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>79.94</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.87</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>11.17</v>
+        <v>11.88</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>317436210.0</t>
+          <t>351042343.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>340905800.4</v>
+        <v>358146601.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>551077334.7</t>
+          <t>483869044.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>219291632.16</v>
+        <v>223785701.76</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-210171534</t>
+          <t>-125722443</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>46395526.40315542</t>
+          <t>36642132.94028828</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-13079245.47872597</t>
+          <t>-17001531.10548103</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>317436210.0</t>
+          <t>351042343.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>181.71</t>
+          <t>209.76</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1920.967</t>
+          <t>2777.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,177 +2911,177 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>115.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-38.14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-35.32</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>44.85</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/07/09</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/03/26</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>2025-12-02 00:00:00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>45.23</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/07/09</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/03/26</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,75 +3092,75 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-5.75</v>
+        <v>3.77</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>10.02</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>111.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>99.02</v>
+        <v>101.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>78.81999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.02</v>
+        <v>11.85</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>199148037.0</t>
+          <t>317436210.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>375506393.4</v>
+        <v>340905800.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>580585132.5</t>
+          <t>551077334.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>215093497.88</v>
+        <v>219291632.16</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-205078739</t>
+          <t>-210171534</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>57209121.29077021</t>
+          <t>46395526.40315542</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-3408207.280549884</t>
+          <t>-13079245.47872597</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>199148037.0</t>
+          <t>317436210.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>156.10</t>
+          <t>181.71</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3681.336</t>
+          <t>1920.967</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.85</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,75 +3579,75 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-8.130000000000001</v>
+        <v>-5.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.23</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>97.39</v>
+        <v>99.02</v>
       </c>
       <c r="BA7" t="n">
-        <v>77.8</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>12.3</v>
+        <v>11.27</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.21</v>
+        <v>12.02</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>390079006.0</t>
+          <t>199148037.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>457066679.2</v>
+        <v>375506393.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>624826119.2</t>
+          <t>580585132.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>211265158</v>
+        <v>215093497.88</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-167759440</t>
+          <t>-205078739</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>68230453.75828296</t>
+          <t>57209121.29077021</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>23203016.08400708</t>
+          <t>-3408207.280549884</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>390079006.0</t>
+          <t>199148037.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>153.66</t>
+          <t>156.10</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4731.625</t>
+          <t>3681.336</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-26.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,75 +4066,75 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.87</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>20.95</v>
+        <v>16.23</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>95.48999999999999</v>
+        <v>97.39</v>
       </c>
       <c r="BA8" t="n">
-        <v>76.70999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>64.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>13.54</v>
+        <v>12.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>532759803.4</v>
+        <v>457066679.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>644573649.4</t>
+          <t>624826119.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>203514658.18</v>
+        <v>211265158</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-111813846</t>
+          <t>-167759440</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>76417260.6081513</t>
+          <t>68230453.75828296</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>39933480.78037387</t>
+          <t>23203016.08400708</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>533027412.0</t>
+          <t>390079006.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>179.27</t>
+          <t>153.66</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2274.683</t>
+          <t>4731.625</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>58.37</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>48.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,75 +4553,75 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.38</v>
+        <v>-0.87</v>
       </c>
       <c r="AV9" t="n">
-        <v>24.93</v>
+        <v>20.95</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>115.9</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>92.78</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>75.31</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>13.86</v>
+        <v>13.54</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.85</v>
+        <v>12.19</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>609591487.8</v>
+        <v>532759803.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>631262663.6</t>
+          <t>644573649.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>192933562.72</v>
+        <v>203514658.18</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-21671175</t>
+          <t>-111813846</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>83050675.12229265</t>
+          <t>76417260.6081513</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>47092048.24731314</t>
+          <t>39933480.78037387</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>264838337.0</t>
+          <t>533027412.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>186.59</t>
+          <t>179.27</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4247.311</t>
+          <t>2274.683</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>62.52</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,75 +5040,75 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>97.28</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>94.43</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="AV10" t="n">
-        <v>26.38</v>
+        <v>24.93</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>89.89</v>
+        <v>92.78</v>
       </c>
       <c r="BA10" t="n">
-        <v>73.78</v>
+        <v>75.31</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>13.75</v>
+        <v>13.86</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.35</v>
+        <v>11.85</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>42517061.96926229</t>
+          <t>43438636.09815951</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>761248869</v>
+        <v>609591487.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>670874203.7</t>
+          <t>631262663.6</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>187661356.84</v>
+        <v>192933562.72</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>90374665</t>
+          <t>-21671175</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>89588607.28137983</t>
+          <t>83050675.12229265</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>84371258.084108</t>
+          <t>47092048.24731314</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>490439175.0</t>
+          <t>264838337.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>182.93</t>
+          <t>186.59</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>147.75</t>
+          <t>137.64</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,42 +5331,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1217.042</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1205.381</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-31.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.61</v>
+        <v>-1.36</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.28</v>
+        <v>-1.04</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>52.78000000000001</t>
+          <t>52.82000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>53.46</v>
+        <v>53.38</v>
       </c>
       <c r="BA11" t="n">
-        <v>54.74</v>
+        <v>54.58</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>59.16</t>
+          <t>58.92</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-109.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>63546872.0</t>
+          <t>64221938.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>68325271.40000001</v>
+        <v>73719849.40000001</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>56049463.1</t>
+          <t>58943781.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>68877612.31999999</v>
+        <v>69021156.72</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>12275808</t>
+          <t>14776068</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1707769.864980638</t>
+          <t>-1184866.983799931</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1808364.879999377</t>
+          <t>1691098.862693958</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>63546872.0</t>
+          <t>64221938.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-24.49</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1001.906</t>
+          <t>1205.381</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.76</v>
+        <v>0.61</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.58</v>
+        <v>-1.28</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.78000000000001</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>53.54</v>
+        <v>53.46</v>
       </c>
       <c r="BA12" t="n">
-        <v>54.89</v>
+        <v>54.74</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.16</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.6</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.67</v>
+        <v>-0.65</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-109.62</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>53038707.0</t>
+          <t>63546872.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>66160708</v>
+        <v>68325271.40000001</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>55912240.3</t>
+          <t>56049463.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>69453118.3</v>
+        <v>68877612.31999999</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>10248467</t>
+          <t>12275808</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2347067.091340641</t>
+          <t>-1707769.864980638</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1983631.801864296</t>
+          <t>1808364.879999377</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>53038707.0</t>
+          <t>63546872.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2401.338</t>
+          <t>1001.906</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,38 +6501,38 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -6541,26 +6541,26 @@
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>53.52</v>
+        <v>53.54</v>
       </c>
       <c r="BA13" t="n">
-        <v>55.03</v>
+        <v>54.89</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>59.61</t>
+          <t>59.37</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-109.89</t>
+          <t>-109.62</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>128355810.0</t>
+          <t>53038707.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>64220047</v>
+        <v>66160708</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>54551291.2</t>
+          <t>55912240.3</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>69959828.64</v>
+        <v>69453118.3</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>9668755</t>
+          <t>10248467</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-3134466.890105174</t>
+          <t>-2347067.091340641</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>3289043.947319031</t>
+          <t>1983631.801864296</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>128355810.0</t>
+          <t>53038707.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1128.585</t>
+          <t>2401.338</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-30.25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.6</v>
+        <v>-1.53</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>52.68000000000001</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>53.54</v>
+        <v>53.52</v>
       </c>
       <c r="BA14" t="n">
-        <v>55.21</v>
+        <v>55.03</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>59.91</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-110.06</t>
+          <t>-109.89</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>59435920.0</t>
+          <t>128355810.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>46846616</v>
+        <v>64220047</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>45326784.0</t>
+          <t>54551291.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>68837502.5</v>
+        <v>69959828.64</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>1519832</t>
+          <t>9668755</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4302377.95145503</t>
+          <t>-3134466.890105174</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-3033237.021578461</t>
+          <t>3289043.947319031</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>59435920.0</t>
+          <t>128355810.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>711.499</t>
+          <t>1128.585</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-31.44</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.7</v>
+        <v>0.61</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.36</v>
+        <v>-1.6</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.68000000000001</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>53.53</v>
+        <v>53.54</v>
       </c>
       <c r="BA15" t="n">
-        <v>55.37</v>
+        <v>55.21</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>59.91</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-110.06</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>37249048.0</t>
+          <t>59435920.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>44167713</v>
+        <v>46846616</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>45002856.4</t>
+          <t>45326784.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>69116768.45999999</v>
+        <v>68837502.5</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-835143</t>
+          <t>1519832</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-4533130.847796224</t>
+          <t>-4302377.95145503</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-4572463.15494708</t>
+          <t>-3033237.021578461</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>37249048.0</t>
+          <t>59435920.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-24.78</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1007.736</t>
+          <t>711.499</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-31.44</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,12 +7962,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7981,44 +7981,44 @@
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.27</v>
+        <v>-1.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.34</v>
+        <v>-1.36</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>53.56</v>
+        <v>53.53</v>
       </c>
       <c r="BA16" t="n">
-        <v>55.53</v>
+        <v>55.37</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.61</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BE16" t="n">
         <v>-0.72</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-110.33</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>52724055.0</t>
+          <t>37249048.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>43773654.8</v>
+        <v>44167713</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>45227977.6</t>
+          <t>45002856.4</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>69838946.16</v>
+        <v>69116768.45999999</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-1454322</t>
+          <t>-835143</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-4525979.519223342</t>
+          <t>-4533130.847796224</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-4230890.51851128</t>
+          <t>-4572463.15494708</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>52724055.0</t>
+          <t>37249048.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-24.78</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>809.469</t>
+          <t>1007.736</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.48</v>
+        <v>-1.27</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.59</v>
+        <v>-0.34</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>53.58</v>
+        <v>53.56</v>
       </c>
       <c r="BA17" t="n">
-        <v>55.68</v>
+        <v>55.53</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.57</v>
+        <v>-0.61</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-110.75</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>45663772.6</v>
+        <v>43773654.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>43887254.7</t>
+          <t>45227977.6</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>70595577.38</v>
+        <v>69838946.16</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>1776517</t>
+          <t>-1454322</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-4579632.064807353</t>
+          <t>-4525979.519223342</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-5249862.840799026</t>
+          <t>-4230890.51851128</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>43335402.0</t>
+          <t>52724055.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>784.817</t>
+          <t>809.469</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-29.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-2.41</v>
+        <v>-1.48</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.66</v>
+        <v>53.58</v>
       </c>
       <c r="BA18" t="n">
-        <v>55.83</v>
+        <v>55.68</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-111.39</t>
+          <t>-110.75</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>44882535.4</v>
+        <v>45663772.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>44153034.1</t>
+          <t>43887254.7</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>71382431.34</v>
+        <v>70595577.38</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>1776517</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-4457771.923717958</t>
+          <t>-4579632.064807353</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-5512115.378324404</t>
+          <t>-5249862.840799026</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>41488655.0</t>
+          <t>43335402.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
           <t>54.2</t>
         </is>
       </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>847.176</t>
+          <t>784.817</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-30.38</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.78</v>
+        <v>-2.41</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.68</v>
+        <v>53.66</v>
       </c>
       <c r="BA19" t="n">
-        <v>56</v>
+        <v>55.83</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-112.22</t>
+          <t>-111.39</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>701654341.9487705</t>
+          <t>700416465.803681</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>43806952</v>
+        <v>44882535.4</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>47872049.3</t>
+          <t>44153034.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>71746544.26000001</v>
+        <v>71382431.34</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-4065097</t>
+          <t>729501</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-4266073.113789514</t>
+          <t>-4457771.923717958</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-5492034.846991934</t>
+          <t>-5512115.378324404</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>46041405.0</t>
+          <t>41488655.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>127396.434</t>
+          <t>112790.098</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.29</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>88.54</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>74.84</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.61</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>18.33</v>
+        <v>5.18</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.26</v>
+        <v>15.9</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>47.07</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>41.93</v>
+        <v>42.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>40.65</v>
+        <v>40.83</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>154.82</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-77.21</t>
+          <t>-68.34</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>6820687164.0</t>
+          <t>6079205405.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2696041633.4</v>
+        <v>3880338143</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1529339880.9</t>
+          <t>2064766016.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>607014963.9</v>
+        <v>683951362.46</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>1166701752</t>
+          <t>1815572126</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>175737404.7074862</t>
+          <t>288538676.0684437</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>725641930.2492876</t>
+          <t>908945668.5537095</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>6820687164.0</t>
+          <t>6079205405.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>51.2</t>
         </is>
       </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>83779.541</t>
+          <t>127396.434</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>48.74</t>
+          <t>76.29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10416,47 +10416,47 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>14.89</v>
+        <v>18.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>7.25</v>
+        <v>12.26</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>47.07</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>41.14</v>
+        <v>41.93</v>
       </c>
       <c r="BA21" t="n">
-        <v>40.33</v>
+        <v>40.65</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>157.56</t>
+          <t>154.82</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1.48</v>
+        <v>2.39</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-86.03</t>
+          <t>-77.21</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>4137211057.0</t>
+          <t>6820687164.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>1363071362.6</v>
+        <v>2696041633.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>916429660.6</t>
+          <t>1529339880.9</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>481812681.56</v>
+        <v>607014963.9</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>446641701</t>
+          <t>1166701752</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>75754763.69988593</t>
+          <t>175737404.7074862</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>358419189.5554962</t>
+          <t>725641930.2492876</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>4137211057.0</t>
+          <t>6820687164.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
           <t>50.7</t>
         </is>
       </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>46.55</t>
-        </is>
-      </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33489.271</t>
+          <t>83779.541</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,177 +10703,177 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>48.74</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>46.1</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>9.98</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>38.55</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2025/04/09</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
         <is>
           <t>2026-01-05 00:00:00</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2025/04/09</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-01-02 00:00:00</t>
-        </is>
-      </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>65.76</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,51 +10899,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>9.27</v>
+        <v>14.89</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.9</v>
+        <v>7.25</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>40.6</v>
+        <v>41.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>40.07</v>
+        <v>40.33</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>132.01</t>
+          <t>157.56</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-86.03</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>1518087925.0</t>
+          <t>4137211057.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>602305833</v>
+        <v>1363071362.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>534676615.7</t>
+          <t>916429660.6</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>403088648.8</v>
+        <v>481812681.56</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>67629217</t>
+          <t>446641701</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>24361231.7261386</t>
+          <t>75754763.69988593</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>108529886.1159553</t>
+          <t>358419189.5554962</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>1518087925.0</t>
+          <t>4137211057.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20045.708</t>
+          <t>33489.271</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,22 +11200,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-15.68</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>26.29</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11386,51 +11386,51 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>81.98</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>2.29</v>
+        <v>9.27</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.84</v>
+        <v>3.9</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41.01000000000001</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>40.27</v>
+        <v>40.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>39.92</v>
+        <v>40.07</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>132.01</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-94.33</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>846499164.0</t>
+          <t>1518087925.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>332357117.8</v>
+        <v>602305833</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>394143159.9</t>
+          <t>534676615.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>375094315.86</v>
+        <v>403088648.8</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-61786042</t>
+          <t>67629217</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>9057840.018899202</t>
+          <t>24361231.7261386</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>28289435.1267556</t>
+          <t>108529886.1159553</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>846499164.0</t>
+          <t>1518087925.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3860.221</t>
+          <t>20045.708</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-24.97</t>
+          <t>-15.68</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>81.98</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.42</v>
+        <v>2.29</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>41.01000000000001</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>40.16</v>
+        <v>40.27</v>
       </c>
       <c r="BA24" t="n">
-        <v>39.85</v>
+        <v>39.92</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-95.39</t>
+          <t>-94.33</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>157722857.0</t>
+          <t>846499164.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>249193889.8</v>
+        <v>332357117.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>332141196.6</t>
+          <t>394143159.9</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>362488533.18</v>
+        <v>375094315.86</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-82947306</t>
+          <t>-61786042</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>5561186.362925313</t>
+          <t>9057840.018899202</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-15394178.86234254</t>
+          <t>28289435.1267556</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>157722857.0</t>
+          <t>846499164.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3822.13</t>
+          <t>3860.221</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>-24.97</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>73.42</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>40.11</v>
+        <v>40.16</v>
       </c>
       <c r="BA25" t="n">
-        <v>39.81</v>
+        <v>39.85</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-95.39</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>155835810.0</t>
+          <t>157722857.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>362638128.4</v>
+        <v>249193889.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>343674934.8</t>
+          <t>332141196.6</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>363315796.84</v>
+        <v>362488533.18</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>18963193</t>
+          <t>-82947306</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>9371252.767519468</t>
+          <t>5561186.362925313</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-3452088.137399018</t>
+          <t>-15394178.86234254</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>155835810.0</t>
+          <t>157722857.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8066.275</t>
+          <t>3822.13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,22 +12806,22 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>40.02</v>
+        <v>40.11</v>
       </c>
       <c r="BA26" t="n">
-        <v>39.77</v>
+        <v>39.81</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>108.24</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>469787958.6</v>
+        <v>362638128.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>345844403.0</t>
+          <t>343674934.8</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>364415966.86</v>
+        <v>363315796.84</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>123943555</t>
+          <t>18963193</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>11702769.29568647</t>
+          <t>9371252.767519468</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>13933513.93885595</t>
+          <t>-3452088.137399018</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>333383409.0</t>
+          <t>155835810.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,17 +13076,17 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4167.968</t>
+          <t>8066.275</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13293,92 +13293,92 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-1.45</v>
+        <v>0.05</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>39.98</v>
+        <v>40.02</v>
       </c>
       <c r="BA27" t="n">
-        <v>39.74</v>
+        <v>39.77</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>129.54</t>
+          <t>108.24</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>467047398.4</v>
+        <v>469787958.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>346645174.9</t>
+          <t>345844403.0</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>361420707.74</v>
+        <v>364415966.86</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>120402223</t>
+          <t>123943555</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>11297179.36056474</t>
+          <t>11702769.29568647</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>19249505.79997534</t>
+          <t>13933513.93885595</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>168344349.0</t>
+          <t>333383409.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10398.551</t>
+          <t>4167.968</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>651</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>62.16</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.37</v>
+        <v>-1.45</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>39.94</v>
+        <v>39.98</v>
       </c>
       <c r="BA28" t="n">
-        <v>39.71</v>
+        <v>39.74</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>261.75</t>
+          <t>129.54</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-98.51</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>327389967.3872951</t>
+          <t>345368327.5920245</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>455929202</v>
+        <v>467047398.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>394210697.6</t>
+          <t>346645174.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>365467847.18</v>
+        <v>361420707.74</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>61718504</t>
+          <t>120402223</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>9851301.826126453</t>
+          <t>11297179.36056474</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>43839053.96586108</t>
+          <t>19249505.79997534</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>430683024.0</t>
+          <t>168344349.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
